--- a/data/outplanting/Sequim/size_Sequim.xlsx
+++ b/data/outplanting/Sequim/size_Sequim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/project-gigas-conditioning/data/outplanting/Sequim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51319906-5D66-9041-8E8F-C77448A62E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FF2B26-9820-6944-9C89-EA43E63467A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="760" windowWidth="27240" windowHeight="16440" xr2:uid="{5AFCA48F-D700-7D47-8B25-C3B58D75E14E}"/>
+    <workbookView xWindow="2180" yWindow="760" windowWidth="16300" windowHeight="16940" xr2:uid="{5AFCA48F-D700-7D47-8B25-C3B58D75E14E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="44">
   <si>
     <t>site</t>
   </si>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -193,6 +193,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -553,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10834F7D-261D-2847-9A91-6E077483AEC7}">
-  <dimension ref="A1:G666"/>
+  <dimension ref="A1:G940"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -14072,7 +14078,5488 @@
         <v>69.304000000000002</v>
       </c>
     </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A667" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667">
+        <v>20260531</v>
+      </c>
+      <c r="C667" t="s">
+        <v>38</v>
+      </c>
+      <c r="D667">
+        <v>1</v>
+      </c>
+      <c r="E667">
+        <v>100.77</v>
+      </c>
+      <c r="F667">
+        <v>54.561</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A668" t="s">
+        <v>6</v>
+      </c>
+      <c r="B668">
+        <v>20260531</v>
+      </c>
+      <c r="C668" t="s">
+        <v>38</v>
+      </c>
+      <c r="D668">
+        <v>2</v>
+      </c>
+      <c r="E668">
+        <v>99.158000000000001</v>
+      </c>
+      <c r="F668">
+        <v>55.744999999999997</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A669" t="s">
+        <v>6</v>
+      </c>
+      <c r="B669">
+        <v>20260531</v>
+      </c>
+      <c r="C669" t="s">
+        <v>38</v>
+      </c>
+      <c r="D669">
+        <v>3</v>
+      </c>
+      <c r="E669">
+        <v>99.036000000000001</v>
+      </c>
+      <c r="F669">
+        <v>47.372</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A670" t="s">
+        <v>6</v>
+      </c>
+      <c r="B670">
+        <v>20260531</v>
+      </c>
+      <c r="C670" t="s">
+        <v>38</v>
+      </c>
+      <c r="D670">
+        <v>4</v>
+      </c>
+      <c r="E670">
+        <v>105.22199999999999</v>
+      </c>
+      <c r="F670">
+        <v>65.378</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A671" t="s">
+        <v>6</v>
+      </c>
+      <c r="B671">
+        <v>20260531</v>
+      </c>
+      <c r="C671" t="s">
+        <v>38</v>
+      </c>
+      <c r="D671">
+        <v>5</v>
+      </c>
+      <c r="E671">
+        <v>99.561000000000007</v>
+      </c>
+      <c r="F671">
+        <v>47.475999999999999</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A672" t="s">
+        <v>6</v>
+      </c>
+      <c r="B672">
+        <v>20260531</v>
+      </c>
+      <c r="C672" t="s">
+        <v>38</v>
+      </c>
+      <c r="D672">
+        <v>6</v>
+      </c>
+      <c r="E672">
+        <v>71.021000000000001</v>
+      </c>
+      <c r="F672">
+        <v>46.029000000000003</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A673" t="s">
+        <v>6</v>
+      </c>
+      <c r="B673">
+        <v>20260531</v>
+      </c>
+      <c r="C673" t="s">
+        <v>38</v>
+      </c>
+      <c r="D673">
+        <v>7</v>
+      </c>
+      <c r="E673">
+        <v>84.718000000000004</v>
+      </c>
+      <c r="F673">
+        <v>59.112000000000002</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A674" t="s">
+        <v>6</v>
+      </c>
+      <c r="B674">
+        <v>20260531</v>
+      </c>
+      <c r="C674" t="s">
+        <v>38</v>
+      </c>
+      <c r="D674">
+        <v>8</v>
+      </c>
+      <c r="E674">
+        <v>90.42</v>
+      </c>
+      <c r="F674">
+        <v>48.302999999999997</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A675" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675">
+        <v>20260531</v>
+      </c>
+      <c r="C675" t="s">
+        <v>38</v>
+      </c>
+      <c r="D675">
+        <v>9</v>
+      </c>
+      <c r="E675">
+        <v>95.778000000000006</v>
+      </c>
+      <c r="F675">
+        <v>34.567999999999998</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A676" t="s">
+        <v>6</v>
+      </c>
+      <c r="B676">
+        <v>20260531</v>
+      </c>
+      <c r="C676" t="s">
+        <v>38</v>
+      </c>
+      <c r="D676">
+        <v>10</v>
+      </c>
+      <c r="E676">
+        <v>77.861000000000004</v>
+      </c>
+      <c r="F676">
+        <v>45.646000000000001</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A677" t="s">
+        <v>6</v>
+      </c>
+      <c r="B677">
+        <v>20260531</v>
+      </c>
+      <c r="C677" t="s">
+        <v>38</v>
+      </c>
+      <c r="D677">
+        <v>11</v>
+      </c>
+      <c r="E677">
+        <v>104.20099999999999</v>
+      </c>
+      <c r="F677">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A678" t="s">
+        <v>6</v>
+      </c>
+      <c r="B678">
+        <v>20260531</v>
+      </c>
+      <c r="C678" t="s">
+        <v>38</v>
+      </c>
+      <c r="D678">
+        <v>12</v>
+      </c>
+      <c r="E678">
+        <v>107.601</v>
+      </c>
+      <c r="F678">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A679" t="s">
+        <v>6</v>
+      </c>
+      <c r="B679">
+        <v>20260531</v>
+      </c>
+      <c r="C679" t="s">
+        <v>38</v>
+      </c>
+      <c r="D679">
+        <v>13</v>
+      </c>
+      <c r="E679">
+        <v>97.451999999999998</v>
+      </c>
+      <c r="F679">
+        <v>62.506</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A680" t="s">
+        <v>6</v>
+      </c>
+      <c r="B680">
+        <v>20260531</v>
+      </c>
+      <c r="C680" t="s">
+        <v>38</v>
+      </c>
+      <c r="D680">
+        <v>14</v>
+      </c>
+      <c r="E680">
+        <v>87.799000000000007</v>
+      </c>
+      <c r="F680">
+        <v>42.045000000000002</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A681" t="s">
+        <v>6</v>
+      </c>
+      <c r="B681">
+        <v>20260531</v>
+      </c>
+      <c r="C681" t="s">
+        <v>38</v>
+      </c>
+      <c r="D681">
+        <v>15</v>
+      </c>
+      <c r="E681">
+        <v>106.529</v>
+      </c>
+      <c r="F681">
+        <v>63.817</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A682" t="s">
+        <v>6</v>
+      </c>
+      <c r="B682">
+        <v>20260531</v>
+      </c>
+      <c r="C682" t="s">
+        <v>38</v>
+      </c>
+      <c r="D682">
+        <v>16</v>
+      </c>
+      <c r="E682">
+        <v>108.895</v>
+      </c>
+      <c r="F682">
+        <v>58.24</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A683" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683">
+        <v>20260531</v>
+      </c>
+      <c r="C683" t="s">
+        <v>38</v>
+      </c>
+      <c r="D683">
+        <v>17</v>
+      </c>
+      <c r="E683">
+        <v>72.852999999999994</v>
+      </c>
+      <c r="F683">
+        <v>44.13</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A684" t="s">
+        <v>6</v>
+      </c>
+      <c r="B684">
+        <v>20260531</v>
+      </c>
+      <c r="C684" t="s">
+        <v>38</v>
+      </c>
+      <c r="D684">
+        <v>18</v>
+      </c>
+      <c r="E684">
+        <v>93.212999999999994</v>
+      </c>
+      <c r="F684">
+        <v>60.279000000000003</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A685" t="s">
+        <v>6</v>
+      </c>
+      <c r="B685">
+        <v>20260531</v>
+      </c>
+      <c r="C685" t="s">
+        <v>38</v>
+      </c>
+      <c r="D685">
+        <v>19</v>
+      </c>
+      <c r="E685">
+        <v>75.986000000000004</v>
+      </c>
+      <c r="F685">
+        <v>54.25</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A686" t="s">
+        <v>6</v>
+      </c>
+      <c r="B686">
+        <v>20260531</v>
+      </c>
+      <c r="C686" t="s">
+        <v>38</v>
+      </c>
+      <c r="D686">
+        <v>20</v>
+      </c>
+      <c r="E686">
+        <v>102.188</v>
+      </c>
+      <c r="F686">
+        <v>60.744</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A687" t="s">
+        <v>6</v>
+      </c>
+      <c r="B687">
+        <v>20260531</v>
+      </c>
+      <c r="C687" t="s">
+        <v>38</v>
+      </c>
+      <c r="D687">
+        <v>21</v>
+      </c>
+      <c r="E687">
+        <v>115.288</v>
+      </c>
+      <c r="F687">
+        <v>57.661000000000001</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A688" t="s">
+        <v>6</v>
+      </c>
+      <c r="B688">
+        <v>20260531</v>
+      </c>
+      <c r="C688" t="s">
+        <v>38</v>
+      </c>
+      <c r="D688">
+        <v>22</v>
+      </c>
+      <c r="E688">
+        <v>69.724999999999994</v>
+      </c>
+      <c r="F688">
+        <v>43.988999999999997</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A689" t="s">
+        <v>6</v>
+      </c>
+      <c r="B689">
+        <v>20260531</v>
+      </c>
+      <c r="C689" t="s">
+        <v>38</v>
+      </c>
+      <c r="D689">
+        <v>23</v>
+      </c>
+      <c r="E689">
+        <v>92.11</v>
+      </c>
+      <c r="F689">
+        <v>49.89</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A690" t="s">
+        <v>6</v>
+      </c>
+      <c r="B690">
+        <v>20260531</v>
+      </c>
+      <c r="C690" t="s">
+        <v>38</v>
+      </c>
+      <c r="D690">
+        <v>24</v>
+      </c>
+      <c r="E690">
+        <v>101.67</v>
+      </c>
+      <c r="F690">
+        <v>26.966000000000001</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A691" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691">
+        <v>20260531</v>
+      </c>
+      <c r="C691" t="s">
+        <v>38</v>
+      </c>
+      <c r="D691">
+        <v>25</v>
+      </c>
+      <c r="E691">
+        <v>113.5</v>
+      </c>
+      <c r="F691">
+        <v>69.075999999999993</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A692" t="s">
+        <v>6</v>
+      </c>
+      <c r="B692">
+        <v>20260531</v>
+      </c>
+      <c r="C692" t="s">
+        <v>38</v>
+      </c>
+      <c r="D692">
+        <v>26</v>
+      </c>
+      <c r="E692">
+        <v>110.014</v>
+      </c>
+      <c r="F692">
+        <v>62.101999999999997</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A693" t="s">
+        <v>6</v>
+      </c>
+      <c r="B693">
+        <v>20260531</v>
+      </c>
+      <c r="C693" t="s">
+        <v>38</v>
+      </c>
+      <c r="D693">
+        <v>27</v>
+      </c>
+      <c r="E693">
+        <v>78.475999999999999</v>
+      </c>
+      <c r="F693">
+        <v>37.770000000000003</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A694" t="s">
+        <v>6</v>
+      </c>
+      <c r="B694">
+        <v>20260531</v>
+      </c>
+      <c r="C694" t="s">
+        <v>38</v>
+      </c>
+      <c r="D694">
+        <v>28</v>
+      </c>
+      <c r="E694">
+        <v>91.120999999999995</v>
+      </c>
+      <c r="F694">
+        <v>56.087000000000003</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A695" t="s">
+        <v>6</v>
+      </c>
+      <c r="B695">
+        <v>20260531</v>
+      </c>
+      <c r="C695" t="s">
+        <v>38</v>
+      </c>
+      <c r="D695">
+        <v>29</v>
+      </c>
+      <c r="E695">
+        <v>134.27500000000001</v>
+      </c>
+      <c r="F695">
+        <v>61.201000000000001</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A696" t="s">
+        <v>6</v>
+      </c>
+      <c r="B696">
+        <v>20260531</v>
+      </c>
+      <c r="C696" t="s">
+        <v>38</v>
+      </c>
+      <c r="D696">
+        <v>30</v>
+      </c>
+      <c r="E696">
+        <v>110.97199999999999</v>
+      </c>
+      <c r="F696">
+        <v>66.599000000000004</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A697" t="s">
+        <v>6</v>
+      </c>
+      <c r="B697">
+        <v>20260531</v>
+      </c>
+      <c r="C697" t="s">
+        <v>38</v>
+      </c>
+      <c r="D697">
+        <v>31</v>
+      </c>
+      <c r="E697">
+        <v>99.826999999999998</v>
+      </c>
+      <c r="F697">
+        <v>59.213000000000001</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A698" t="s">
+        <v>6</v>
+      </c>
+      <c r="B698">
+        <v>20260531</v>
+      </c>
+      <c r="C698" t="s">
+        <v>38</v>
+      </c>
+      <c r="D698">
+        <v>32</v>
+      </c>
+      <c r="E698">
+        <v>94.866</v>
+      </c>
+      <c r="F698">
+        <v>58.912999999999997</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A699" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699">
+        <v>20260531</v>
+      </c>
+      <c r="C699" t="s">
+        <v>38</v>
+      </c>
+      <c r="D699">
+        <v>33</v>
+      </c>
+      <c r="E699">
+        <v>105.648</v>
+      </c>
+      <c r="F699">
+        <v>63.692999999999998</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A700" t="s">
+        <v>6</v>
+      </c>
+      <c r="B700">
+        <v>20260531</v>
+      </c>
+      <c r="C700" t="s">
+        <v>38</v>
+      </c>
+      <c r="D700">
+        <v>34</v>
+      </c>
+      <c r="E700">
+        <v>100.01300000000001</v>
+      </c>
+      <c r="F700">
+        <v>59.780999999999999</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A701" t="s">
+        <v>6</v>
+      </c>
+      <c r="B701">
+        <v>20260531</v>
+      </c>
+      <c r="C701" t="s">
+        <v>38</v>
+      </c>
+      <c r="D701">
+        <v>35</v>
+      </c>
+      <c r="E701">
+        <v>102.292</v>
+      </c>
+      <c r="F701">
+        <v>52.127000000000002</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A702" t="s">
+        <v>6</v>
+      </c>
+      <c r="B702">
+        <v>20260531</v>
+      </c>
+      <c r="C702" t="s">
+        <v>38</v>
+      </c>
+      <c r="D702">
+        <v>36</v>
+      </c>
+      <c r="E702">
+        <v>114.501</v>
+      </c>
+      <c r="F702">
+        <v>67.191999999999993</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A703" t="s">
+        <v>6</v>
+      </c>
+      <c r="B703">
+        <v>20260531</v>
+      </c>
+      <c r="C703" t="s">
+        <v>38</v>
+      </c>
+      <c r="D703">
+        <v>37</v>
+      </c>
+      <c r="E703">
+        <v>101.241</v>
+      </c>
+      <c r="F703">
+        <v>67.341999999999999</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A704" t="s">
+        <v>6</v>
+      </c>
+      <c r="B704">
+        <v>20260531</v>
+      </c>
+      <c r="C704" t="s">
+        <v>38</v>
+      </c>
+      <c r="D704">
+        <v>38</v>
+      </c>
+      <c r="E704">
+        <v>87.141000000000005</v>
+      </c>
+      <c r="F704">
+        <v>60.616999999999997</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A705" t="s">
+        <v>6</v>
+      </c>
+      <c r="B705">
+        <v>20260531</v>
+      </c>
+      <c r="C705" t="s">
+        <v>38</v>
+      </c>
+      <c r="D705">
+        <v>39</v>
+      </c>
+      <c r="E705">
+        <v>68.745999999999995</v>
+      </c>
+      <c r="F705">
+        <v>38.762999999999998</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A706" t="s">
+        <v>6</v>
+      </c>
+      <c r="B706">
+        <v>20260531</v>
+      </c>
+      <c r="C706" t="s">
+        <v>39</v>
+      </c>
+      <c r="D706">
+        <v>1</v>
+      </c>
+      <c r="E706">
+        <v>97.930999999999997</v>
+      </c>
+      <c r="F706">
+        <v>50.71</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A707" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707">
+        <v>20260531</v>
+      </c>
+      <c r="C707" t="s">
+        <v>39</v>
+      </c>
+      <c r="D707">
+        <v>2</v>
+      </c>
+      <c r="E707">
+        <v>102.654</v>
+      </c>
+      <c r="F707">
+        <v>56.451999999999998</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A708" t="s">
+        <v>6</v>
+      </c>
+      <c r="B708">
+        <v>20260531</v>
+      </c>
+      <c r="C708" t="s">
+        <v>39</v>
+      </c>
+      <c r="D708">
+        <v>3</v>
+      </c>
+      <c r="E708">
+        <v>95.242000000000004</v>
+      </c>
+      <c r="F708">
+        <v>64.787000000000006</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A709" t="s">
+        <v>6</v>
+      </c>
+      <c r="B709">
+        <v>20260531</v>
+      </c>
+      <c r="C709" t="s">
+        <v>39</v>
+      </c>
+      <c r="D709">
+        <v>4</v>
+      </c>
+      <c r="E709">
+        <v>108.352</v>
+      </c>
+      <c r="F709">
+        <v>60.454999999999998</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A710" t="s">
+        <v>6</v>
+      </c>
+      <c r="B710">
+        <v>20260531</v>
+      </c>
+      <c r="C710" t="s">
+        <v>39</v>
+      </c>
+      <c r="D710">
+        <v>5</v>
+      </c>
+      <c r="E710">
+        <v>117.76600000000001</v>
+      </c>
+      <c r="F710">
+        <v>53.981999999999999</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A711" t="s">
+        <v>6</v>
+      </c>
+      <c r="B711">
+        <v>20260531</v>
+      </c>
+      <c r="C711" t="s">
+        <v>39</v>
+      </c>
+      <c r="D711">
+        <v>6</v>
+      </c>
+      <c r="E711">
+        <v>107.53400000000001</v>
+      </c>
+      <c r="F711">
+        <v>53.718000000000004</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A712" t="s">
+        <v>6</v>
+      </c>
+      <c r="B712">
+        <v>20260531</v>
+      </c>
+      <c r="C712" t="s">
+        <v>39</v>
+      </c>
+      <c r="D712">
+        <v>7</v>
+      </c>
+      <c r="E712">
+        <v>109.119</v>
+      </c>
+      <c r="F712">
+        <v>49.881</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A713" t="s">
+        <v>6</v>
+      </c>
+      <c r="B713">
+        <v>20260531</v>
+      </c>
+      <c r="C713" t="s">
+        <v>39</v>
+      </c>
+      <c r="D713">
+        <v>8</v>
+      </c>
+      <c r="E713">
+        <v>112.398</v>
+      </c>
+      <c r="F713">
+        <v>73.944000000000003</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A714" t="s">
+        <v>6</v>
+      </c>
+      <c r="B714">
+        <v>20260531</v>
+      </c>
+      <c r="C714" t="s">
+        <v>39</v>
+      </c>
+      <c r="D714">
+        <v>9</v>
+      </c>
+      <c r="E714">
+        <v>98.045000000000002</v>
+      </c>
+      <c r="F714">
+        <v>52.777999999999999</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A715" t="s">
+        <v>6</v>
+      </c>
+      <c r="B715">
+        <v>20260531</v>
+      </c>
+      <c r="C715" t="s">
+        <v>39</v>
+      </c>
+      <c r="D715">
+        <v>10</v>
+      </c>
+      <c r="E715">
+        <v>60.246000000000002</v>
+      </c>
+      <c r="F715">
+        <v>38.581000000000003</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A716" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716">
+        <v>20260531</v>
+      </c>
+      <c r="C716" t="s">
+        <v>39</v>
+      </c>
+      <c r="D716">
+        <v>11</v>
+      </c>
+      <c r="E716">
+        <v>59.598999999999997</v>
+      </c>
+      <c r="F716">
+        <v>37.393999999999998</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A717" t="s">
+        <v>6</v>
+      </c>
+      <c r="B717">
+        <v>20260531</v>
+      </c>
+      <c r="C717" t="s">
+        <v>39</v>
+      </c>
+      <c r="D717">
+        <v>12</v>
+      </c>
+      <c r="E717">
+        <v>103.31100000000001</v>
+      </c>
+      <c r="F717">
+        <v>55.606000000000002</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A718" t="s">
+        <v>6</v>
+      </c>
+      <c r="B718">
+        <v>20260531</v>
+      </c>
+      <c r="C718" t="s">
+        <v>39</v>
+      </c>
+      <c r="D718">
+        <v>13</v>
+      </c>
+      <c r="E718">
+        <v>112.023</v>
+      </c>
+      <c r="F718">
+        <v>36.494</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A719" t="s">
+        <v>6</v>
+      </c>
+      <c r="B719">
+        <v>20260531</v>
+      </c>
+      <c r="C719" t="s">
+        <v>39</v>
+      </c>
+      <c r="D719">
+        <v>14</v>
+      </c>
+      <c r="E719">
+        <v>70.212000000000003</v>
+      </c>
+      <c r="F719">
+        <v>36.204999999999998</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A720" t="s">
+        <v>6</v>
+      </c>
+      <c r="B720">
+        <v>20260531</v>
+      </c>
+      <c r="C720" t="s">
+        <v>39</v>
+      </c>
+      <c r="D720">
+        <v>15</v>
+      </c>
+      <c r="E720">
+        <v>78.066999999999993</v>
+      </c>
+      <c r="F720">
+        <v>40.514000000000003</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A721" t="s">
+        <v>6</v>
+      </c>
+      <c r="B721">
+        <v>20260531</v>
+      </c>
+      <c r="C721" t="s">
+        <v>39</v>
+      </c>
+      <c r="D721">
+        <v>16</v>
+      </c>
+      <c r="E721">
+        <v>121.16500000000001</v>
+      </c>
+      <c r="F721">
+        <v>64.721000000000004</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A722" t="s">
+        <v>6</v>
+      </c>
+      <c r="B722">
+        <v>20260531</v>
+      </c>
+      <c r="C722" t="s">
+        <v>39</v>
+      </c>
+      <c r="D722">
+        <v>17</v>
+      </c>
+      <c r="E722">
+        <v>118.291</v>
+      </c>
+      <c r="F722">
+        <v>42.762</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A723" t="s">
+        <v>6</v>
+      </c>
+      <c r="B723">
+        <v>20260531</v>
+      </c>
+      <c r="C723" t="s">
+        <v>39</v>
+      </c>
+      <c r="D723">
+        <v>18</v>
+      </c>
+      <c r="E723">
+        <v>87.72</v>
+      </c>
+      <c r="F723">
+        <v>45.167000000000002</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A724" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724">
+        <v>20260531</v>
+      </c>
+      <c r="C724" t="s">
+        <v>39</v>
+      </c>
+      <c r="D724">
+        <v>19</v>
+      </c>
+      <c r="E724">
+        <v>114.172</v>
+      </c>
+      <c r="F724">
+        <v>60.433</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A725" t="s">
+        <v>6</v>
+      </c>
+      <c r="B725">
+        <v>20260531</v>
+      </c>
+      <c r="C725" t="s">
+        <v>39</v>
+      </c>
+      <c r="D725">
+        <v>20</v>
+      </c>
+      <c r="E725">
+        <v>91.561999999999998</v>
+      </c>
+      <c r="F725">
+        <v>33.963000000000001</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A726" t="s">
+        <v>6</v>
+      </c>
+      <c r="B726">
+        <v>20260531</v>
+      </c>
+      <c r="C726" t="s">
+        <v>39</v>
+      </c>
+      <c r="D726">
+        <v>21</v>
+      </c>
+      <c r="E726">
+        <v>80.248000000000005</v>
+      </c>
+      <c r="F726">
+        <v>38.81</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A727" t="s">
+        <v>6</v>
+      </c>
+      <c r="B727">
+        <v>20260531</v>
+      </c>
+      <c r="C727" t="s">
+        <v>39</v>
+      </c>
+      <c r="D727">
+        <v>22</v>
+      </c>
+      <c r="E727">
+        <v>89.010999999999996</v>
+      </c>
+      <c r="F727">
+        <v>51.536999999999999</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A728" t="s">
+        <v>6</v>
+      </c>
+      <c r="B728">
+        <v>20260531</v>
+      </c>
+      <c r="C728" t="s">
+        <v>39</v>
+      </c>
+      <c r="D728">
+        <v>23</v>
+      </c>
+      <c r="E728">
+        <v>68.364999999999995</v>
+      </c>
+      <c r="F728">
+        <v>34.689</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A729" t="s">
+        <v>6</v>
+      </c>
+      <c r="B729">
+        <v>20260531</v>
+      </c>
+      <c r="C729" t="s">
+        <v>39</v>
+      </c>
+      <c r="D729">
+        <v>24</v>
+      </c>
+      <c r="E729">
+        <v>109.611</v>
+      </c>
+      <c r="F729">
+        <v>55.365000000000002</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A730" t="s">
+        <v>6</v>
+      </c>
+      <c r="B730">
+        <v>20260531</v>
+      </c>
+      <c r="C730" t="s">
+        <v>39</v>
+      </c>
+      <c r="D730">
+        <v>25</v>
+      </c>
+      <c r="E730">
+        <v>113.925</v>
+      </c>
+      <c r="F730">
+        <v>57.61</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A731" t="s">
+        <v>6</v>
+      </c>
+      <c r="B731">
+        <v>20260531</v>
+      </c>
+      <c r="C731" t="s">
+        <v>39</v>
+      </c>
+      <c r="D731">
+        <v>26</v>
+      </c>
+      <c r="E731">
+        <v>83.921000000000006</v>
+      </c>
+      <c r="F731">
+        <v>29.597999999999999</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A732" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732">
+        <v>20260531</v>
+      </c>
+      <c r="C732" t="s">
+        <v>39</v>
+      </c>
+      <c r="D732">
+        <v>27</v>
+      </c>
+      <c r="E732">
+        <v>66.022000000000006</v>
+      </c>
+      <c r="F732">
+        <v>54.173000000000002</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A733" t="s">
+        <v>6</v>
+      </c>
+      <c r="B733">
+        <v>20260531</v>
+      </c>
+      <c r="C733" t="s">
+        <v>39</v>
+      </c>
+      <c r="D733">
+        <v>28</v>
+      </c>
+      <c r="E733">
+        <v>87.299000000000007</v>
+      </c>
+      <c r="F733">
+        <v>42.186</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A734" t="s">
+        <v>6</v>
+      </c>
+      <c r="B734">
+        <v>20260531</v>
+      </c>
+      <c r="C734" t="s">
+        <v>39</v>
+      </c>
+      <c r="D734">
+        <v>29</v>
+      </c>
+      <c r="E734">
+        <v>51.716000000000001</v>
+      </c>
+      <c r="F734">
+        <v>31.396999999999998</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A735" t="s">
+        <v>6</v>
+      </c>
+      <c r="B735">
+        <v>20260531</v>
+      </c>
+      <c r="C735" t="s">
+        <v>39</v>
+      </c>
+      <c r="D735">
+        <v>30</v>
+      </c>
+      <c r="E735">
+        <v>100.492</v>
+      </c>
+      <c r="F735">
+        <v>42.109000000000002</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A736" t="s">
+        <v>6</v>
+      </c>
+      <c r="B736">
+        <v>20260531</v>
+      </c>
+      <c r="C736" t="s">
+        <v>39</v>
+      </c>
+      <c r="D736">
+        <v>31</v>
+      </c>
+      <c r="E736">
+        <v>108.965</v>
+      </c>
+      <c r="F736">
+        <v>49.243000000000002</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A737" t="s">
+        <v>6</v>
+      </c>
+      <c r="B737">
+        <v>20260531</v>
+      </c>
+      <c r="C737" t="s">
+        <v>39</v>
+      </c>
+      <c r="D737">
+        <v>32</v>
+      </c>
+      <c r="E737">
+        <v>87.332999999999998</v>
+      </c>
+      <c r="F737">
+        <v>45.168999999999997</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A738" t="s">
+        <v>6</v>
+      </c>
+      <c r="B738">
+        <v>20260531</v>
+      </c>
+      <c r="C738" t="s">
+        <v>39</v>
+      </c>
+      <c r="D738">
+        <v>33</v>
+      </c>
+      <c r="E738">
+        <v>98.165000000000006</v>
+      </c>
+      <c r="F738">
+        <v>55.064999999999998</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A739" t="s">
+        <v>6</v>
+      </c>
+      <c r="B739">
+        <v>20260531</v>
+      </c>
+      <c r="C739" t="s">
+        <v>39</v>
+      </c>
+      <c r="D739">
+        <v>34</v>
+      </c>
+      <c r="E739">
+        <v>113.913</v>
+      </c>
+      <c r="F739">
+        <v>61.052999999999997</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A740" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740">
+        <v>20260531</v>
+      </c>
+      <c r="C740" t="s">
+        <v>39</v>
+      </c>
+      <c r="D740">
+        <v>35</v>
+      </c>
+      <c r="E740">
+        <v>95.658000000000001</v>
+      </c>
+      <c r="F740">
+        <v>55.914000000000001</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A741" t="s">
+        <v>6</v>
+      </c>
+      <c r="B741">
+        <v>20260531</v>
+      </c>
+      <c r="C741" t="s">
+        <v>39</v>
+      </c>
+      <c r="D741">
+        <v>36</v>
+      </c>
+      <c r="E741">
+        <v>94.700999999999993</v>
+      </c>
+      <c r="F741">
+        <v>48.484000000000002</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A742" t="s">
+        <v>6</v>
+      </c>
+      <c r="B742">
+        <v>20260531</v>
+      </c>
+      <c r="C742" t="s">
+        <v>39</v>
+      </c>
+      <c r="D742">
+        <v>37</v>
+      </c>
+      <c r="E742">
+        <v>108.095</v>
+      </c>
+      <c r="F742">
+        <v>57.305</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A743" t="s">
+        <v>6</v>
+      </c>
+      <c r="B743">
+        <v>20260531</v>
+      </c>
+      <c r="C743" t="s">
+        <v>39</v>
+      </c>
+      <c r="D743">
+        <v>38</v>
+      </c>
+      <c r="E743">
+        <v>75.382999999999996</v>
+      </c>
+      <c r="F743">
+        <v>30.640999999999998</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A744" t="s">
+        <v>6</v>
+      </c>
+      <c r="B744">
+        <v>20260531</v>
+      </c>
+      <c r="C744" t="s">
+        <v>39</v>
+      </c>
+      <c r="D744">
+        <v>39</v>
+      </c>
+      <c r="E744">
+        <v>52.228999999999999</v>
+      </c>
+      <c r="F744">
+        <v>43.487000000000002</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A745" t="s">
+        <v>6</v>
+      </c>
+      <c r="B745">
+        <v>20260531</v>
+      </c>
+      <c r="C745" t="s">
+        <v>39</v>
+      </c>
+      <c r="D745">
+        <v>40</v>
+      </c>
+      <c r="E745">
+        <v>108.518</v>
+      </c>
+      <c r="F745">
+        <v>49.426000000000002</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A746" t="s">
+        <v>6</v>
+      </c>
+      <c r="B746">
+        <v>20260531</v>
+      </c>
+      <c r="C746" t="s">
+        <v>39</v>
+      </c>
+      <c r="D746">
+        <v>41</v>
+      </c>
+      <c r="E746">
+        <v>89.819000000000003</v>
+      </c>
+      <c r="F746">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A747" t="s">
+        <v>6</v>
+      </c>
+      <c r="B747">
+        <v>20260531</v>
+      </c>
+      <c r="C747" t="s">
+        <v>39</v>
+      </c>
+      <c r="D747">
+        <v>42</v>
+      </c>
+      <c r="E747">
+        <v>115.264</v>
+      </c>
+      <c r="F747">
+        <v>55.783999999999999</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A748" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748">
+        <v>20260531</v>
+      </c>
+      <c r="C748" t="s">
+        <v>39</v>
+      </c>
+      <c r="D748">
+        <v>43</v>
+      </c>
+      <c r="E748">
+        <v>93.578000000000003</v>
+      </c>
+      <c r="F748">
+        <v>62.118000000000002</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A749" t="s">
+        <v>6</v>
+      </c>
+      <c r="B749">
+        <v>20260531</v>
+      </c>
+      <c r="C749" t="s">
+        <v>39</v>
+      </c>
+      <c r="D749">
+        <v>44</v>
+      </c>
+      <c r="E749">
+        <v>105.11499999999999</v>
+      </c>
+      <c r="F749">
+        <v>62.029000000000003</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A750" t="s">
+        <v>6</v>
+      </c>
+      <c r="B750">
+        <v>20260531</v>
+      </c>
+      <c r="C750" t="s">
+        <v>39</v>
+      </c>
+      <c r="D750">
+        <v>45</v>
+      </c>
+      <c r="E750">
+        <v>114.684</v>
+      </c>
+      <c r="F750">
+        <v>51.314</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A751" t="s">
+        <v>6</v>
+      </c>
+      <c r="B751">
+        <v>20260531</v>
+      </c>
+      <c r="C751" t="s">
+        <v>39</v>
+      </c>
+      <c r="D751">
+        <v>46</v>
+      </c>
+      <c r="E751">
+        <v>144.53399999999999</v>
+      </c>
+      <c r="F751">
+        <v>47.503</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A752" t="s">
+        <v>6</v>
+      </c>
+      <c r="B752">
+        <v>20260531</v>
+      </c>
+      <c r="C752" t="s">
+        <v>39</v>
+      </c>
+      <c r="D752">
+        <v>47</v>
+      </c>
+      <c r="E752">
+        <v>135.12299999999999</v>
+      </c>
+      <c r="F752">
+        <v>47.320999999999998</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A753" t="s">
+        <v>6</v>
+      </c>
+      <c r="B753">
+        <v>20260531</v>
+      </c>
+      <c r="C753" t="s">
+        <v>39</v>
+      </c>
+      <c r="D753">
+        <v>48</v>
+      </c>
+      <c r="E753">
+        <v>145.81399999999999</v>
+      </c>
+      <c r="F753">
+        <v>65.608000000000004</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A754" t="s">
+        <v>6</v>
+      </c>
+      <c r="B754">
+        <v>20260531</v>
+      </c>
+      <c r="C754" t="s">
+        <v>39</v>
+      </c>
+      <c r="D754">
+        <v>49</v>
+      </c>
+      <c r="E754">
+        <v>103.91</v>
+      </c>
+      <c r="F754">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A755" t="s">
+        <v>6</v>
+      </c>
+      <c r="B755">
+        <v>20260531</v>
+      </c>
+      <c r="C755" t="s">
+        <v>39</v>
+      </c>
+      <c r="D755">
+        <v>50</v>
+      </c>
+      <c r="E755">
+        <v>87.9</v>
+      </c>
+      <c r="F755">
+        <v>67.143000000000001</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A756" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756">
+        <v>20260531</v>
+      </c>
+      <c r="C756" t="s">
+        <v>23</v>
+      </c>
+      <c r="D756">
+        <v>1</v>
+      </c>
+      <c r="E756">
+        <v>84.751999999999995</v>
+      </c>
+      <c r="F756">
+        <v>42.764000000000003</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A757" t="s">
+        <v>6</v>
+      </c>
+      <c r="B757">
+        <v>20260531</v>
+      </c>
+      <c r="C757" t="s">
+        <v>23</v>
+      </c>
+      <c r="D757">
+        <v>2</v>
+      </c>
+      <c r="E757">
+        <v>81.376000000000005</v>
+      </c>
+      <c r="F757">
+        <v>56.073999999999998</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A758" t="s">
+        <v>6</v>
+      </c>
+      <c r="B758">
+        <v>20260531</v>
+      </c>
+      <c r="C758" t="s">
+        <v>23</v>
+      </c>
+      <c r="D758">
+        <v>3</v>
+      </c>
+      <c r="E758">
+        <v>75.647999999999996</v>
+      </c>
+      <c r="F758">
+        <v>43.673000000000002</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A759" t="s">
+        <v>6</v>
+      </c>
+      <c r="B759">
+        <v>20260531</v>
+      </c>
+      <c r="C759" t="s">
+        <v>23</v>
+      </c>
+      <c r="D759">
+        <v>4</v>
+      </c>
+      <c r="E759">
+        <v>82.572999999999993</v>
+      </c>
+      <c r="F759">
+        <v>32.021999999999998</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A760" t="s">
+        <v>6</v>
+      </c>
+      <c r="B760">
+        <v>20260531</v>
+      </c>
+      <c r="C760" t="s">
+        <v>23</v>
+      </c>
+      <c r="D760">
+        <v>5</v>
+      </c>
+      <c r="E760">
+        <v>88.989000000000004</v>
+      </c>
+      <c r="F760">
+        <v>49.226999999999997</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A761" t="s">
+        <v>6</v>
+      </c>
+      <c r="B761">
+        <v>20260531</v>
+      </c>
+      <c r="C761" t="s">
+        <v>23</v>
+      </c>
+      <c r="D761">
+        <v>6</v>
+      </c>
+      <c r="E761">
+        <v>76.879000000000005</v>
+      </c>
+      <c r="F761">
+        <v>39.110999999999997</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A762" t="s">
+        <v>6</v>
+      </c>
+      <c r="B762">
+        <v>20260531</v>
+      </c>
+      <c r="C762" t="s">
+        <v>23</v>
+      </c>
+      <c r="D762">
+        <v>7</v>
+      </c>
+      <c r="E762">
+        <v>84.828000000000003</v>
+      </c>
+      <c r="F762">
+        <v>40.439</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A763" t="s">
+        <v>6</v>
+      </c>
+      <c r="B763">
+        <v>20260531</v>
+      </c>
+      <c r="C763" t="s">
+        <v>23</v>
+      </c>
+      <c r="D763">
+        <v>8</v>
+      </c>
+      <c r="E763">
+        <v>76.616</v>
+      </c>
+      <c r="F763">
+        <v>46.686999999999998</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A764" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764">
+        <v>20260531</v>
+      </c>
+      <c r="C764" t="s">
+        <v>23</v>
+      </c>
+      <c r="D764">
+        <v>9</v>
+      </c>
+      <c r="E764">
+        <v>95.295000000000002</v>
+      </c>
+      <c r="F764">
+        <v>48.984000000000002</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A765" t="s">
+        <v>6</v>
+      </c>
+      <c r="B765">
+        <v>20260531</v>
+      </c>
+      <c r="C765" t="s">
+        <v>23</v>
+      </c>
+      <c r="D765">
+        <v>10</v>
+      </c>
+      <c r="E765">
+        <v>52.292999999999999</v>
+      </c>
+      <c r="F765">
+        <v>39.570999999999998</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A766" t="s">
+        <v>6</v>
+      </c>
+      <c r="B766">
+        <v>20260531</v>
+      </c>
+      <c r="C766" t="s">
+        <v>23</v>
+      </c>
+      <c r="D766">
+        <v>11</v>
+      </c>
+      <c r="E766">
+        <v>107.551</v>
+      </c>
+      <c r="F766">
+        <v>51.149000000000001</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A767" t="s">
+        <v>6</v>
+      </c>
+      <c r="B767">
+        <v>20260531</v>
+      </c>
+      <c r="C767" t="s">
+        <v>23</v>
+      </c>
+      <c r="D767">
+        <v>12</v>
+      </c>
+      <c r="E767">
+        <v>85.311999999999998</v>
+      </c>
+      <c r="F767">
+        <v>40.594000000000001</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A768" t="s">
+        <v>6</v>
+      </c>
+      <c r="B768">
+        <v>20260531</v>
+      </c>
+      <c r="C768" t="s">
+        <v>23</v>
+      </c>
+      <c r="D768">
+        <v>13</v>
+      </c>
+      <c r="E768">
+        <v>107.568</v>
+      </c>
+      <c r="F768">
+        <v>47.06</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A769" t="s">
+        <v>6</v>
+      </c>
+      <c r="B769">
+        <v>20260531</v>
+      </c>
+      <c r="C769" t="s">
+        <v>23</v>
+      </c>
+      <c r="D769">
+        <v>14</v>
+      </c>
+      <c r="E769">
+        <v>98.022999999999996</v>
+      </c>
+      <c r="F769">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A770" t="s">
+        <v>6</v>
+      </c>
+      <c r="B770">
+        <v>20260531</v>
+      </c>
+      <c r="C770" t="s">
+        <v>23</v>
+      </c>
+      <c r="D770">
+        <v>15</v>
+      </c>
+      <c r="E770">
+        <v>88.977000000000004</v>
+      </c>
+      <c r="F770">
+        <v>48.283999999999999</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A771" t="s">
+        <v>6</v>
+      </c>
+      <c r="B771">
+        <v>20260531</v>
+      </c>
+      <c r="C771" t="s">
+        <v>23</v>
+      </c>
+      <c r="D771">
+        <v>16</v>
+      </c>
+      <c r="E771">
+        <v>93.152000000000001</v>
+      </c>
+      <c r="F771">
+        <v>59.472000000000001</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A772" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772">
+        <v>20260531</v>
+      </c>
+      <c r="C772" t="s">
+        <v>23</v>
+      </c>
+      <c r="D772">
+        <v>17</v>
+      </c>
+      <c r="E772">
+        <v>79.629000000000005</v>
+      </c>
+      <c r="F772">
+        <v>34.804000000000002</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A773" t="s">
+        <v>6</v>
+      </c>
+      <c r="B773">
+        <v>20260531</v>
+      </c>
+      <c r="C773" t="s">
+        <v>23</v>
+      </c>
+      <c r="D773">
+        <v>18</v>
+      </c>
+      <c r="E773">
+        <v>81.543999999999997</v>
+      </c>
+      <c r="F773">
+        <v>52.811</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A774" t="s">
+        <v>6</v>
+      </c>
+      <c r="B774">
+        <v>20260531</v>
+      </c>
+      <c r="C774" t="s">
+        <v>23</v>
+      </c>
+      <c r="D774">
+        <v>19</v>
+      </c>
+      <c r="E774">
+        <v>85.501999999999995</v>
+      </c>
+      <c r="F774">
+        <v>47.64</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A775" t="s">
+        <v>6</v>
+      </c>
+      <c r="B775">
+        <v>20260531</v>
+      </c>
+      <c r="C775" t="s">
+        <v>23</v>
+      </c>
+      <c r="D775">
+        <v>20</v>
+      </c>
+      <c r="E775">
+        <v>73.254000000000005</v>
+      </c>
+      <c r="F775">
+        <v>56.923000000000002</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A776" t="s">
+        <v>6</v>
+      </c>
+      <c r="B776">
+        <v>20260531</v>
+      </c>
+      <c r="C776" t="s">
+        <v>23</v>
+      </c>
+      <c r="D776">
+        <v>21</v>
+      </c>
+      <c r="E776">
+        <v>77.478999999999999</v>
+      </c>
+      <c r="F776">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A777" t="s">
+        <v>6</v>
+      </c>
+      <c r="B777">
+        <v>20260531</v>
+      </c>
+      <c r="C777" t="s">
+        <v>23</v>
+      </c>
+      <c r="D777">
+        <v>22</v>
+      </c>
+      <c r="E777">
+        <v>80.602999999999994</v>
+      </c>
+      <c r="F777">
+        <v>47.289000000000001</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A778" t="s">
+        <v>6</v>
+      </c>
+      <c r="B778">
+        <v>20260531</v>
+      </c>
+      <c r="C778" t="s">
+        <v>23</v>
+      </c>
+      <c r="D778">
+        <v>23</v>
+      </c>
+      <c r="E778">
+        <v>95.497</v>
+      </c>
+      <c r="F778">
+        <v>49.985999999999997</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A779" t="s">
+        <v>6</v>
+      </c>
+      <c r="B779">
+        <v>20260531</v>
+      </c>
+      <c r="C779" t="s">
+        <v>23</v>
+      </c>
+      <c r="D779">
+        <v>24</v>
+      </c>
+      <c r="E779">
+        <v>69.971999999999994</v>
+      </c>
+      <c r="F779">
+        <v>50.795999999999999</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A780" t="s">
+        <v>6</v>
+      </c>
+      <c r="B780">
+        <v>20260531</v>
+      </c>
+      <c r="C780" t="s">
+        <v>23</v>
+      </c>
+      <c r="D780">
+        <v>25</v>
+      </c>
+      <c r="E780">
+        <v>83.793000000000006</v>
+      </c>
+      <c r="F780">
+        <v>44.807000000000002</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A781" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781">
+        <v>20260531</v>
+      </c>
+      <c r="C781" t="s">
+        <v>23</v>
+      </c>
+      <c r="D781">
+        <v>26</v>
+      </c>
+      <c r="E781">
+        <v>81.671999999999997</v>
+      </c>
+      <c r="F781">
+        <v>36.624000000000002</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A782" t="s">
+        <v>6</v>
+      </c>
+      <c r="B782">
+        <v>20260531</v>
+      </c>
+      <c r="C782" t="s">
+        <v>23</v>
+      </c>
+      <c r="D782">
+        <v>27</v>
+      </c>
+      <c r="E782">
+        <v>90.311000000000007</v>
+      </c>
+      <c r="F782">
+        <v>56.036999999999999</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A783" t="s">
+        <v>6</v>
+      </c>
+      <c r="B783">
+        <v>20260531</v>
+      </c>
+      <c r="C783" t="s">
+        <v>23</v>
+      </c>
+      <c r="D783">
+        <v>28</v>
+      </c>
+      <c r="E783">
+        <v>87.98</v>
+      </c>
+      <c r="F783">
+        <v>43.701999999999998</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A784" t="s">
+        <v>6</v>
+      </c>
+      <c r="B784">
+        <v>20260531</v>
+      </c>
+      <c r="C784" t="s">
+        <v>23</v>
+      </c>
+      <c r="D784">
+        <v>29</v>
+      </c>
+      <c r="E784">
+        <v>60.706000000000003</v>
+      </c>
+      <c r="F784">
+        <v>31.645</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A785" t="s">
+        <v>6</v>
+      </c>
+      <c r="B785">
+        <v>20260531</v>
+      </c>
+      <c r="C785" t="s">
+        <v>23</v>
+      </c>
+      <c r="D785">
+        <v>30</v>
+      </c>
+      <c r="E785">
+        <v>71.954999999999998</v>
+      </c>
+      <c r="F785">
+        <v>42.235999999999997</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A786" t="s">
+        <v>6</v>
+      </c>
+      <c r="B786">
+        <v>20260531</v>
+      </c>
+      <c r="C786" t="s">
+        <v>23</v>
+      </c>
+      <c r="D786">
+        <v>31</v>
+      </c>
+      <c r="E786">
+        <v>86.085999999999999</v>
+      </c>
+      <c r="F786">
+        <v>49.078000000000003</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A787" t="s">
+        <v>6</v>
+      </c>
+      <c r="B787">
+        <v>20260531</v>
+      </c>
+      <c r="C787" t="s">
+        <v>23</v>
+      </c>
+      <c r="D787">
+        <v>32</v>
+      </c>
+      <c r="E787">
+        <v>87.186999999999998</v>
+      </c>
+      <c r="F787">
+        <v>46.784999999999997</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A788" t="s">
+        <v>6</v>
+      </c>
+      <c r="B788">
+        <v>20260531</v>
+      </c>
+      <c r="C788" t="s">
+        <v>23</v>
+      </c>
+      <c r="D788">
+        <v>33</v>
+      </c>
+      <c r="E788">
+        <v>96.605000000000004</v>
+      </c>
+      <c r="F788">
+        <v>57.542000000000002</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A789" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789">
+        <v>20260531</v>
+      </c>
+      <c r="C789" t="s">
+        <v>23</v>
+      </c>
+      <c r="D789">
+        <v>34</v>
+      </c>
+      <c r="E789">
+        <v>85.867999999999995</v>
+      </c>
+      <c r="F789">
+        <v>48.167000000000002</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A790" t="s">
+        <v>6</v>
+      </c>
+      <c r="B790">
+        <v>20260531</v>
+      </c>
+      <c r="C790" t="s">
+        <v>23</v>
+      </c>
+      <c r="D790">
+        <v>35</v>
+      </c>
+      <c r="E790">
+        <v>84.893000000000001</v>
+      </c>
+      <c r="F790">
+        <v>42.475000000000001</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A791" t="s">
+        <v>6</v>
+      </c>
+      <c r="B791">
+        <v>20260531</v>
+      </c>
+      <c r="C791" t="s">
+        <v>23</v>
+      </c>
+      <c r="D791">
+        <v>36</v>
+      </c>
+      <c r="E791">
+        <v>89.242999999999995</v>
+      </c>
+      <c r="F791">
+        <v>51.225000000000001</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A792" t="s">
+        <v>6</v>
+      </c>
+      <c r="B792">
+        <v>20260531</v>
+      </c>
+      <c r="C792" t="s">
+        <v>23</v>
+      </c>
+      <c r="D792">
+        <v>37</v>
+      </c>
+      <c r="E792">
+        <v>86.268000000000001</v>
+      </c>
+      <c r="F792">
+        <v>52.210999999999999</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A793" t="s">
+        <v>6</v>
+      </c>
+      <c r="B793">
+        <v>20260531</v>
+      </c>
+      <c r="C793" t="s">
+        <v>23</v>
+      </c>
+      <c r="D793">
+        <v>38</v>
+      </c>
+      <c r="E793">
+        <v>91.988</v>
+      </c>
+      <c r="F793">
+        <v>48.792000000000002</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A794" t="s">
+        <v>6</v>
+      </c>
+      <c r="B794">
+        <v>20260531</v>
+      </c>
+      <c r="C794" t="s">
+        <v>23</v>
+      </c>
+      <c r="D794">
+        <v>39</v>
+      </c>
+      <c r="E794">
+        <v>89.625</v>
+      </c>
+      <c r="F794">
+        <v>43.837000000000003</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A795" t="s">
+        <v>6</v>
+      </c>
+      <c r="B795">
+        <v>20260531</v>
+      </c>
+      <c r="C795" t="s">
+        <v>23</v>
+      </c>
+      <c r="D795">
+        <v>40</v>
+      </c>
+      <c r="E795">
+        <v>108.242</v>
+      </c>
+      <c r="F795">
+        <v>51.125</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A796" t="s">
+        <v>6</v>
+      </c>
+      <c r="B796">
+        <v>20260531</v>
+      </c>
+      <c r="C796" t="s">
+        <v>23</v>
+      </c>
+      <c r="D796">
+        <v>41</v>
+      </c>
+      <c r="E796">
+        <v>83.022000000000006</v>
+      </c>
+      <c r="F796">
+        <v>51.893999999999998</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A797" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797">
+        <v>20260531</v>
+      </c>
+      <c r="C797" t="s">
+        <v>23</v>
+      </c>
+      <c r="D797">
+        <v>42</v>
+      </c>
+      <c r="E797">
+        <v>89.263000000000005</v>
+      </c>
+      <c r="F797">
+        <v>42.430999999999997</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A798" t="s">
+        <v>6</v>
+      </c>
+      <c r="B798">
+        <v>20260531</v>
+      </c>
+      <c r="C798" t="s">
+        <v>23</v>
+      </c>
+      <c r="D798">
+        <v>43</v>
+      </c>
+      <c r="E798">
+        <v>74.031999999999996</v>
+      </c>
+      <c r="F798">
+        <v>44.378999999999998</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A799" t="s">
+        <v>6</v>
+      </c>
+      <c r="B799">
+        <v>20260531</v>
+      </c>
+      <c r="C799" t="s">
+        <v>23</v>
+      </c>
+      <c r="D799">
+        <v>44</v>
+      </c>
+      <c r="E799">
+        <v>63.472999999999999</v>
+      </c>
+      <c r="F799">
+        <v>25.707000000000001</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A800" t="s">
+        <v>6</v>
+      </c>
+      <c r="B800">
+        <v>20260531</v>
+      </c>
+      <c r="C800" t="s">
+        <v>23</v>
+      </c>
+      <c r="D800">
+        <v>45</v>
+      </c>
+      <c r="E800">
+        <v>77.596999999999994</v>
+      </c>
+      <c r="F800">
+        <v>39.615000000000002</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A801" t="s">
+        <v>6</v>
+      </c>
+      <c r="B801">
+        <v>20260531</v>
+      </c>
+      <c r="C801" t="s">
+        <v>23</v>
+      </c>
+      <c r="D801">
+        <v>46</v>
+      </c>
+      <c r="E801">
+        <v>70.084999999999994</v>
+      </c>
+      <c r="F801">
+        <v>40.652999999999999</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A802" t="s">
+        <v>6</v>
+      </c>
+      <c r="B802">
+        <v>20260531</v>
+      </c>
+      <c r="C802" t="s">
+        <v>23</v>
+      </c>
+      <c r="D802">
+        <v>47</v>
+      </c>
+      <c r="E802">
+        <v>79.384</v>
+      </c>
+      <c r="F802">
+        <v>38.768999999999998</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A803" t="s">
+        <v>6</v>
+      </c>
+      <c r="B803">
+        <v>20260531</v>
+      </c>
+      <c r="C803" t="s">
+        <v>23</v>
+      </c>
+      <c r="D803">
+        <v>48</v>
+      </c>
+      <c r="E803">
+        <v>78.013000000000005</v>
+      </c>
+      <c r="F803">
+        <v>63.348999999999997</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A804" t="s">
+        <v>6</v>
+      </c>
+      <c r="B804">
+        <v>20260531</v>
+      </c>
+      <c r="C804" t="s">
+        <v>23</v>
+      </c>
+      <c r="D804">
+        <v>49</v>
+      </c>
+      <c r="E804">
+        <v>84.445999999999998</v>
+      </c>
+      <c r="F804">
+        <v>52.334000000000003</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A805" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805">
+        <v>20260531</v>
+      </c>
+      <c r="C805" t="s">
+        <v>23</v>
+      </c>
+      <c r="D805">
+        <v>50</v>
+      </c>
+      <c r="E805">
+        <v>82.783000000000001</v>
+      </c>
+      <c r="F805">
+        <v>51.585000000000001</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A806" t="s">
+        <v>6</v>
+      </c>
+      <c r="B806">
+        <v>20260531</v>
+      </c>
+      <c r="C806" t="s">
+        <v>23</v>
+      </c>
+      <c r="D806">
+        <v>51</v>
+      </c>
+      <c r="E806">
+        <v>72.903999999999996</v>
+      </c>
+      <c r="F806">
+        <v>35.936999999999998</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A807" t="s">
+        <v>6</v>
+      </c>
+      <c r="B807">
+        <v>20260531</v>
+      </c>
+      <c r="C807" t="s">
+        <v>40</v>
+      </c>
+      <c r="D807">
+        <v>1</v>
+      </c>
+      <c r="E807">
+        <v>76.957999999999998</v>
+      </c>
+      <c r="F807">
+        <v>23.913</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A808" t="s">
+        <v>6</v>
+      </c>
+      <c r="B808">
+        <v>20260531</v>
+      </c>
+      <c r="C808" t="s">
+        <v>40</v>
+      </c>
+      <c r="D808">
+        <v>2</v>
+      </c>
+      <c r="E808">
+        <v>110.021</v>
+      </c>
+      <c r="F808">
+        <v>63.158000000000001</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A809" t="s">
+        <v>6</v>
+      </c>
+      <c r="B809">
+        <v>20260531</v>
+      </c>
+      <c r="C809" t="s">
+        <v>40</v>
+      </c>
+      <c r="D809">
+        <v>3</v>
+      </c>
+      <c r="E809">
+        <v>121.053</v>
+      </c>
+      <c r="F809">
+        <v>57.948</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A810" t="s">
+        <v>6</v>
+      </c>
+      <c r="B810">
+        <v>20260531</v>
+      </c>
+      <c r="C810" t="s">
+        <v>40</v>
+      </c>
+      <c r="D810">
+        <v>4</v>
+      </c>
+      <c r="E810">
+        <v>90.302000000000007</v>
+      </c>
+      <c r="F810">
+        <v>47.466000000000001</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A811" t="s">
+        <v>6</v>
+      </c>
+      <c r="B811">
+        <v>20260531</v>
+      </c>
+      <c r="C811" t="s">
+        <v>40</v>
+      </c>
+      <c r="D811">
+        <v>5</v>
+      </c>
+      <c r="E811">
+        <v>104.364</v>
+      </c>
+      <c r="F811">
+        <v>55.354999999999997</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A812" t="s">
+        <v>6</v>
+      </c>
+      <c r="B812">
+        <v>20260531</v>
+      </c>
+      <c r="C812" t="s">
+        <v>40</v>
+      </c>
+      <c r="D812">
+        <v>6</v>
+      </c>
+      <c r="E812">
+        <v>71.995000000000005</v>
+      </c>
+      <c r="F812">
+        <v>29.646000000000001</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A813" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813">
+        <v>20260531</v>
+      </c>
+      <c r="C813" t="s">
+        <v>40</v>
+      </c>
+      <c r="D813">
+        <v>7</v>
+      </c>
+      <c r="E813">
+        <v>91.135000000000005</v>
+      </c>
+      <c r="F813">
+        <v>46.512</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A814" t="s">
+        <v>6</v>
+      </c>
+      <c r="B814">
+        <v>20260531</v>
+      </c>
+      <c r="C814" t="s">
+        <v>40</v>
+      </c>
+      <c r="D814">
+        <v>8</v>
+      </c>
+      <c r="E814">
+        <v>101.492</v>
+      </c>
+      <c r="F814">
+        <v>52.825000000000003</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A815" t="s">
+        <v>6</v>
+      </c>
+      <c r="B815">
+        <v>20260531</v>
+      </c>
+      <c r="C815" t="s">
+        <v>40</v>
+      </c>
+      <c r="D815">
+        <v>9</v>
+      </c>
+      <c r="E815">
+        <v>93.634</v>
+      </c>
+      <c r="F815">
+        <v>51.585999999999999</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A816" t="s">
+        <v>6</v>
+      </c>
+      <c r="B816">
+        <v>20260531</v>
+      </c>
+      <c r="C816" t="s">
+        <v>40</v>
+      </c>
+      <c r="D816">
+        <v>10</v>
+      </c>
+      <c r="E816">
+        <v>92.156000000000006</v>
+      </c>
+      <c r="F816">
+        <v>62.354999999999997</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A817" t="s">
+        <v>6</v>
+      </c>
+      <c r="B817">
+        <v>20260531</v>
+      </c>
+      <c r="C817" t="s">
+        <v>40</v>
+      </c>
+      <c r="D817">
+        <v>11</v>
+      </c>
+      <c r="E817">
+        <v>115.386</v>
+      </c>
+      <c r="F817">
+        <v>51.332000000000001</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A818" t="s">
+        <v>6</v>
+      </c>
+      <c r="B818">
+        <v>20260531</v>
+      </c>
+      <c r="C818" t="s">
+        <v>40</v>
+      </c>
+      <c r="D818">
+        <v>12</v>
+      </c>
+      <c r="E818">
+        <v>110.069</v>
+      </c>
+      <c r="F818">
+        <v>33.088000000000001</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A819" t="s">
+        <v>6</v>
+      </c>
+      <c r="B819">
+        <v>20260531</v>
+      </c>
+      <c r="C819" t="s">
+        <v>40</v>
+      </c>
+      <c r="D819">
+        <v>13</v>
+      </c>
+      <c r="E819">
+        <v>87.686000000000007</v>
+      </c>
+      <c r="F819">
+        <v>28.93</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A820" t="s">
+        <v>6</v>
+      </c>
+      <c r="B820">
+        <v>20260531</v>
+      </c>
+      <c r="C820" t="s">
+        <v>40</v>
+      </c>
+      <c r="D820">
+        <v>14</v>
+      </c>
+      <c r="E820">
+        <v>110.58</v>
+      </c>
+      <c r="F820">
+        <v>49.030999999999999</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A821" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821">
+        <v>20260531</v>
+      </c>
+      <c r="C821" t="s">
+        <v>40</v>
+      </c>
+      <c r="D821">
+        <v>15</v>
+      </c>
+      <c r="E821">
+        <v>81.257999999999996</v>
+      </c>
+      <c r="F821">
+        <v>57.000999999999998</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A822" t="s">
+        <v>6</v>
+      </c>
+      <c r="B822">
+        <v>20260531</v>
+      </c>
+      <c r="C822" t="s">
+        <v>40</v>
+      </c>
+      <c r="D822">
+        <v>16</v>
+      </c>
+      <c r="E822">
+        <v>120.256</v>
+      </c>
+      <c r="F822">
+        <v>47.194000000000003</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A823" t="s">
+        <v>6</v>
+      </c>
+      <c r="B823">
+        <v>20260531</v>
+      </c>
+      <c r="C823" t="s">
+        <v>40</v>
+      </c>
+      <c r="D823">
+        <v>17</v>
+      </c>
+      <c r="E823">
+        <v>120.97799999999999</v>
+      </c>
+      <c r="F823">
+        <v>67.671000000000006</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A824" t="s">
+        <v>6</v>
+      </c>
+      <c r="B824">
+        <v>20260531</v>
+      </c>
+      <c r="C824" t="s">
+        <v>40</v>
+      </c>
+      <c r="D824">
+        <v>18</v>
+      </c>
+      <c r="E824">
+        <v>105.251</v>
+      </c>
+      <c r="F824">
+        <v>47.034999999999997</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A825" t="s">
+        <v>6</v>
+      </c>
+      <c r="B825">
+        <v>20260531</v>
+      </c>
+      <c r="C825" t="s">
+        <v>40</v>
+      </c>
+      <c r="D825">
+        <v>19</v>
+      </c>
+      <c r="E825">
+        <v>108.13800000000001</v>
+      </c>
+      <c r="F825">
+        <v>43.930999999999997</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A826" t="s">
+        <v>6</v>
+      </c>
+      <c r="B826">
+        <v>20260531</v>
+      </c>
+      <c r="C826" t="s">
+        <v>40</v>
+      </c>
+      <c r="D826">
+        <v>20</v>
+      </c>
+      <c r="E826">
+        <v>92.308999999999997</v>
+      </c>
+      <c r="F826">
+        <v>63.978000000000002</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A827" t="s">
+        <v>6</v>
+      </c>
+      <c r="B827">
+        <v>20260531</v>
+      </c>
+      <c r="C827" t="s">
+        <v>40</v>
+      </c>
+      <c r="D827">
+        <v>21</v>
+      </c>
+      <c r="E827">
+        <v>77.533000000000001</v>
+      </c>
+      <c r="F827">
+        <v>53.615000000000002</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A828" t="s">
+        <v>6</v>
+      </c>
+      <c r="B828">
+        <v>20260531</v>
+      </c>
+      <c r="C828" t="s">
+        <v>40</v>
+      </c>
+      <c r="D828">
+        <v>22</v>
+      </c>
+      <c r="E828">
+        <v>105.077</v>
+      </c>
+      <c r="F828">
+        <v>47.012999999999998</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A829" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829">
+        <v>20260531</v>
+      </c>
+      <c r="C829" t="s">
+        <v>40</v>
+      </c>
+      <c r="D829">
+        <v>23</v>
+      </c>
+      <c r="E829">
+        <v>109.77500000000001</v>
+      </c>
+      <c r="F829">
+        <v>60.143000000000001</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A830" t="s">
+        <v>6</v>
+      </c>
+      <c r="B830">
+        <v>20260531</v>
+      </c>
+      <c r="C830" t="s">
+        <v>40</v>
+      </c>
+      <c r="D830">
+        <v>24</v>
+      </c>
+      <c r="E830">
+        <v>104.321</v>
+      </c>
+      <c r="F830">
+        <v>48.433</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A831" t="s">
+        <v>6</v>
+      </c>
+      <c r="B831">
+        <v>20260531</v>
+      </c>
+      <c r="C831" t="s">
+        <v>40</v>
+      </c>
+      <c r="D831">
+        <v>25</v>
+      </c>
+      <c r="E831">
+        <v>90.766999999999996</v>
+      </c>
+      <c r="F831">
+        <v>48.064</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A832" t="s">
+        <v>6</v>
+      </c>
+      <c r="B832">
+        <v>20260531</v>
+      </c>
+      <c r="C832" t="s">
+        <v>40</v>
+      </c>
+      <c r="D832">
+        <v>26</v>
+      </c>
+      <c r="E832">
+        <v>122.881</v>
+      </c>
+      <c r="F832">
+        <v>56.432000000000002</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A833" t="s">
+        <v>6</v>
+      </c>
+      <c r="B833">
+        <v>20260531</v>
+      </c>
+      <c r="C833" t="s">
+        <v>40</v>
+      </c>
+      <c r="D833">
+        <v>27</v>
+      </c>
+      <c r="E833">
+        <v>103.998</v>
+      </c>
+      <c r="F833">
+        <v>46.515000000000001</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A834" t="s">
+        <v>6</v>
+      </c>
+      <c r="B834">
+        <v>20260531</v>
+      </c>
+      <c r="C834" t="s">
+        <v>40</v>
+      </c>
+      <c r="D834">
+        <v>28</v>
+      </c>
+      <c r="E834">
+        <v>91.674000000000007</v>
+      </c>
+      <c r="F834">
+        <v>40.569000000000003</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A835" t="s">
+        <v>6</v>
+      </c>
+      <c r="B835">
+        <v>20260531</v>
+      </c>
+      <c r="C835" t="s">
+        <v>40</v>
+      </c>
+      <c r="D835">
+        <v>29</v>
+      </c>
+      <c r="E835">
+        <v>88.022999999999996</v>
+      </c>
+      <c r="F835">
+        <v>47.238999999999997</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A836" t="s">
+        <v>6</v>
+      </c>
+      <c r="B836">
+        <v>20260531</v>
+      </c>
+      <c r="C836" t="s">
+        <v>40</v>
+      </c>
+      <c r="D836">
+        <v>30</v>
+      </c>
+      <c r="E836">
+        <v>83.61</v>
+      </c>
+      <c r="F836">
+        <v>55.216000000000001</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A837" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837">
+        <v>20260531</v>
+      </c>
+      <c r="C837" t="s">
+        <v>40</v>
+      </c>
+      <c r="D837">
+        <v>31</v>
+      </c>
+      <c r="E837">
+        <v>101.608</v>
+      </c>
+      <c r="F837">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A838" t="s">
+        <v>6</v>
+      </c>
+      <c r="B838">
+        <v>20260531</v>
+      </c>
+      <c r="C838" t="s">
+        <v>40</v>
+      </c>
+      <c r="D838">
+        <v>32</v>
+      </c>
+      <c r="E838">
+        <v>81.165000000000006</v>
+      </c>
+      <c r="F838">
+        <v>48.366</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A839" t="s">
+        <v>6</v>
+      </c>
+      <c r="B839">
+        <v>20260531</v>
+      </c>
+      <c r="C839" t="s">
+        <v>40</v>
+      </c>
+      <c r="D839">
+        <v>33</v>
+      </c>
+      <c r="E839">
+        <v>125.93</v>
+      </c>
+      <c r="F839">
+        <v>49.997</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A840" t="s">
+        <v>6</v>
+      </c>
+      <c r="B840">
+        <v>20260531</v>
+      </c>
+      <c r="C840" t="s">
+        <v>40</v>
+      </c>
+      <c r="D840">
+        <v>34</v>
+      </c>
+      <c r="E840">
+        <v>97.563000000000002</v>
+      </c>
+      <c r="F840">
+        <v>51.24</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A841" t="s">
+        <v>6</v>
+      </c>
+      <c r="B841">
+        <v>20260531</v>
+      </c>
+      <c r="C841" t="s">
+        <v>40</v>
+      </c>
+      <c r="D841">
+        <v>35</v>
+      </c>
+      <c r="E841">
+        <v>114.892</v>
+      </c>
+      <c r="F841">
+        <v>55.070999999999998</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A842" t="s">
+        <v>6</v>
+      </c>
+      <c r="B842">
+        <v>20260531</v>
+      </c>
+      <c r="C842" t="s">
+        <v>40</v>
+      </c>
+      <c r="D842">
+        <v>36</v>
+      </c>
+      <c r="E842">
+        <v>111.553</v>
+      </c>
+      <c r="F842">
+        <v>55.616</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A843" t="s">
+        <v>6</v>
+      </c>
+      <c r="B843">
+        <v>20260531</v>
+      </c>
+      <c r="C843" t="s">
+        <v>40</v>
+      </c>
+      <c r="D843">
+        <v>37</v>
+      </c>
+      <c r="E843">
+        <v>119.018</v>
+      </c>
+      <c r="F843">
+        <v>53.524999999999999</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A844" t="s">
+        <v>6</v>
+      </c>
+      <c r="B844">
+        <v>20260531</v>
+      </c>
+      <c r="C844" t="s">
+        <v>40</v>
+      </c>
+      <c r="D844">
+        <v>38</v>
+      </c>
+      <c r="E844">
+        <v>116.71899999999999</v>
+      </c>
+      <c r="F844">
+        <v>48.451000000000001</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A845" t="s">
+        <v>6</v>
+      </c>
+      <c r="B845">
+        <v>20260531</v>
+      </c>
+      <c r="C845" t="s">
+        <v>40</v>
+      </c>
+      <c r="D845">
+        <v>39</v>
+      </c>
+      <c r="E845">
+        <v>98.891000000000005</v>
+      </c>
+      <c r="F845">
+        <v>39.94</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A846" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846">
+        <v>20260531</v>
+      </c>
+      <c r="C846" t="s">
+        <v>40</v>
+      </c>
+      <c r="D846">
+        <v>40</v>
+      </c>
+      <c r="E846">
+        <v>104.43600000000001</v>
+      </c>
+      <c r="F846">
+        <v>55.728000000000002</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A847" t="s">
+        <v>6</v>
+      </c>
+      <c r="B847">
+        <v>20260531</v>
+      </c>
+      <c r="C847" t="s">
+        <v>40</v>
+      </c>
+      <c r="D847">
+        <v>41</v>
+      </c>
+      <c r="E847">
+        <v>116.69499999999999</v>
+      </c>
+      <c r="F847">
+        <v>63.81</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A848" t="s">
+        <v>6</v>
+      </c>
+      <c r="B848">
+        <v>20260531</v>
+      </c>
+      <c r="C848" t="s">
+        <v>40</v>
+      </c>
+      <c r="D848">
+        <v>42</v>
+      </c>
+      <c r="E848">
+        <v>115.099</v>
+      </c>
+      <c r="F848">
+        <v>69.378</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A849" t="s">
+        <v>6</v>
+      </c>
+      <c r="B849">
+        <v>20260531</v>
+      </c>
+      <c r="C849" t="s">
+        <v>15</v>
+      </c>
+      <c r="D849">
+        <v>1</v>
+      </c>
+      <c r="E849">
+        <v>67.003</v>
+      </c>
+      <c r="F849">
+        <v>40.003</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A850" t="s">
+        <v>6</v>
+      </c>
+      <c r="B850">
+        <v>20260531</v>
+      </c>
+      <c r="C850" t="s">
+        <v>15</v>
+      </c>
+      <c r="D850">
+        <v>2</v>
+      </c>
+      <c r="E850">
+        <v>99.474999999999994</v>
+      </c>
+      <c r="F850">
+        <v>50.741</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A851" t="s">
+        <v>6</v>
+      </c>
+      <c r="B851">
+        <v>20260531</v>
+      </c>
+      <c r="C851" t="s">
+        <v>15</v>
+      </c>
+      <c r="D851">
+        <v>3</v>
+      </c>
+      <c r="E851">
+        <v>74.350999999999999</v>
+      </c>
+      <c r="F851">
+        <v>25.416</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A852" t="s">
+        <v>6</v>
+      </c>
+      <c r="B852">
+        <v>20260531</v>
+      </c>
+      <c r="C852" t="s">
+        <v>15</v>
+      </c>
+      <c r="D852">
+        <v>4</v>
+      </c>
+      <c r="E852">
+        <v>101.291</v>
+      </c>
+      <c r="F852">
+        <v>36.939</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A853" t="s">
+        <v>6</v>
+      </c>
+      <c r="B853">
+        <v>20260531</v>
+      </c>
+      <c r="C853" t="s">
+        <v>15</v>
+      </c>
+      <c r="D853">
+        <v>5</v>
+      </c>
+      <c r="E853">
+        <v>106.758</v>
+      </c>
+      <c r="F853">
+        <v>36.201999999999998</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A854" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854">
+        <v>20260531</v>
+      </c>
+      <c r="C854" t="s">
+        <v>15</v>
+      </c>
+      <c r="D854">
+        <v>6</v>
+      </c>
+      <c r="E854">
+        <v>87.319000000000003</v>
+      </c>
+      <c r="F854">
+        <v>51.442</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A855" t="s">
+        <v>6</v>
+      </c>
+      <c r="B855">
+        <v>20260531</v>
+      </c>
+      <c r="C855" t="s">
+        <v>15</v>
+      </c>
+      <c r="D855">
+        <v>7</v>
+      </c>
+      <c r="E855">
+        <v>104.637</v>
+      </c>
+      <c r="F855">
+        <v>54.021999999999998</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A856" t="s">
+        <v>6</v>
+      </c>
+      <c r="B856">
+        <v>20260531</v>
+      </c>
+      <c r="C856" t="s">
+        <v>15</v>
+      </c>
+      <c r="D856">
+        <v>8</v>
+      </c>
+      <c r="E856">
+        <v>94.084999999999994</v>
+      </c>
+      <c r="F856">
+        <v>23.292999999999999</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A857" t="s">
+        <v>6</v>
+      </c>
+      <c r="B857">
+        <v>20260531</v>
+      </c>
+      <c r="C857" t="s">
+        <v>15</v>
+      </c>
+      <c r="D857">
+        <v>9</v>
+      </c>
+      <c r="E857">
+        <v>74.236999999999995</v>
+      </c>
+      <c r="F857">
+        <v>28.972999999999999</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A858" t="s">
+        <v>6</v>
+      </c>
+      <c r="B858">
+        <v>20260531</v>
+      </c>
+      <c r="C858" t="s">
+        <v>15</v>
+      </c>
+      <c r="D858">
+        <v>10</v>
+      </c>
+      <c r="E858">
+        <v>80.069999999999993</v>
+      </c>
+      <c r="F858">
+        <v>33.143000000000001</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A859" t="s">
+        <v>6</v>
+      </c>
+      <c r="B859">
+        <v>20260531</v>
+      </c>
+      <c r="C859" t="s">
+        <v>15</v>
+      </c>
+      <c r="D859">
+        <v>11</v>
+      </c>
+      <c r="E859">
+        <v>87.173000000000002</v>
+      </c>
+      <c r="F859">
+        <v>44.465000000000003</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A860" t="s">
+        <v>6</v>
+      </c>
+      <c r="B860">
+        <v>20260531</v>
+      </c>
+      <c r="C860" t="s">
+        <v>15</v>
+      </c>
+      <c r="D860">
+        <v>12</v>
+      </c>
+      <c r="E860">
+        <v>86.575000000000003</v>
+      </c>
+      <c r="F860">
+        <v>53.807000000000002</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A861" t="s">
+        <v>6</v>
+      </c>
+      <c r="B861">
+        <v>20260531</v>
+      </c>
+      <c r="C861" t="s">
+        <v>15</v>
+      </c>
+      <c r="D861">
+        <v>13</v>
+      </c>
+      <c r="E861">
+        <v>92.216999999999999</v>
+      </c>
+      <c r="F861">
+        <v>50.37</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A862" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862">
+        <v>20260531</v>
+      </c>
+      <c r="C862" t="s">
+        <v>15</v>
+      </c>
+      <c r="D862">
+        <v>14</v>
+      </c>
+      <c r="E862">
+        <v>68.262</v>
+      </c>
+      <c r="F862">
+        <v>40.981999999999999</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A863" t="s">
+        <v>6</v>
+      </c>
+      <c r="B863">
+        <v>20260531</v>
+      </c>
+      <c r="C863" t="s">
+        <v>15</v>
+      </c>
+      <c r="D863">
+        <v>15</v>
+      </c>
+      <c r="E863">
+        <v>70.793000000000006</v>
+      </c>
+      <c r="F863">
+        <v>45.661999999999999</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A864" t="s">
+        <v>6</v>
+      </c>
+      <c r="B864">
+        <v>20260531</v>
+      </c>
+      <c r="C864" t="s">
+        <v>15</v>
+      </c>
+      <c r="D864">
+        <v>16</v>
+      </c>
+      <c r="E864">
+        <v>77.603999999999999</v>
+      </c>
+      <c r="F864">
+        <v>43.271999999999998</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A865" t="s">
+        <v>6</v>
+      </c>
+      <c r="B865">
+        <v>20260531</v>
+      </c>
+      <c r="C865" t="s">
+        <v>15</v>
+      </c>
+      <c r="D865">
+        <v>17</v>
+      </c>
+      <c r="E865">
+        <v>93.47</v>
+      </c>
+      <c r="F865">
+        <v>32.149000000000001</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A866" t="s">
+        <v>6</v>
+      </c>
+      <c r="B866">
+        <v>20260531</v>
+      </c>
+      <c r="C866" t="s">
+        <v>15</v>
+      </c>
+      <c r="D866">
+        <v>18</v>
+      </c>
+      <c r="E866">
+        <v>69.144999999999996</v>
+      </c>
+      <c r="F866">
+        <v>43.351999999999997</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A867" t="s">
+        <v>6</v>
+      </c>
+      <c r="B867">
+        <v>20260531</v>
+      </c>
+      <c r="C867" t="s">
+        <v>15</v>
+      </c>
+      <c r="D867">
+        <v>19</v>
+      </c>
+      <c r="E867">
+        <v>69.144999999999996</v>
+      </c>
+      <c r="F867">
+        <v>43.351999999999997</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A868" t="s">
+        <v>6</v>
+      </c>
+      <c r="B868">
+        <v>20260531</v>
+      </c>
+      <c r="C868" t="s">
+        <v>15</v>
+      </c>
+      <c r="D868">
+        <v>20</v>
+      </c>
+      <c r="E868">
+        <v>77.5</v>
+      </c>
+      <c r="F868">
+        <v>42.912999999999997</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A869" t="s">
+        <v>6</v>
+      </c>
+      <c r="B869">
+        <v>20260531</v>
+      </c>
+      <c r="C869" t="s">
+        <v>15</v>
+      </c>
+      <c r="D869">
+        <v>21</v>
+      </c>
+      <c r="E869">
+        <v>121.068</v>
+      </c>
+      <c r="F869">
+        <v>45.279000000000003</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A870" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870">
+        <v>20260531</v>
+      </c>
+      <c r="C870" t="s">
+        <v>15</v>
+      </c>
+      <c r="D870">
+        <v>22</v>
+      </c>
+      <c r="E870">
+        <v>85.292000000000002</v>
+      </c>
+      <c r="F870">
+        <v>64.162999999999997</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A871" t="s">
+        <v>6</v>
+      </c>
+      <c r="B871">
+        <v>20260531</v>
+      </c>
+      <c r="C871" t="s">
+        <v>15</v>
+      </c>
+      <c r="D871">
+        <v>23</v>
+      </c>
+      <c r="E871">
+        <v>60.125</v>
+      </c>
+      <c r="F871">
+        <v>39.497999999999998</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A872" t="s">
+        <v>6</v>
+      </c>
+      <c r="B872">
+        <v>20260531</v>
+      </c>
+      <c r="C872" t="s">
+        <v>15</v>
+      </c>
+      <c r="D872">
+        <v>24</v>
+      </c>
+      <c r="E872">
+        <v>104.44199999999999</v>
+      </c>
+      <c r="F872">
+        <v>50.173000000000002</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A873" t="s">
+        <v>6</v>
+      </c>
+      <c r="B873">
+        <v>20260531</v>
+      </c>
+      <c r="C873" t="s">
+        <v>15</v>
+      </c>
+      <c r="D873">
+        <v>25</v>
+      </c>
+      <c r="E873">
+        <v>82.102000000000004</v>
+      </c>
+      <c r="F873">
+        <v>45.518000000000001</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A874" t="s">
+        <v>6</v>
+      </c>
+      <c r="B874">
+        <v>20260531</v>
+      </c>
+      <c r="C874" t="s">
+        <v>15</v>
+      </c>
+      <c r="D874">
+        <v>26</v>
+      </c>
+      <c r="E874">
+        <v>82.242999999999995</v>
+      </c>
+      <c r="F874">
+        <v>42.648000000000003</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A875" t="s">
+        <v>6</v>
+      </c>
+      <c r="B875">
+        <v>20260531</v>
+      </c>
+      <c r="C875" t="s">
+        <v>15</v>
+      </c>
+      <c r="D875">
+        <v>27</v>
+      </c>
+      <c r="E875">
+        <v>78.792000000000002</v>
+      </c>
+      <c r="F875">
+        <v>46.276000000000003</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A876" t="s">
+        <v>6</v>
+      </c>
+      <c r="B876">
+        <v>20260531</v>
+      </c>
+      <c r="C876" t="s">
+        <v>15</v>
+      </c>
+      <c r="D876">
+        <v>28</v>
+      </c>
+      <c r="E876">
+        <v>107.809</v>
+      </c>
+      <c r="F876">
+        <v>46.942</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A877" t="s">
+        <v>6</v>
+      </c>
+      <c r="B877">
+        <v>20260531</v>
+      </c>
+      <c r="C877" t="s">
+        <v>15</v>
+      </c>
+      <c r="D877">
+        <v>29</v>
+      </c>
+      <c r="E877">
+        <v>80.641999999999996</v>
+      </c>
+      <c r="F877">
+        <v>43.518999999999998</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A878" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878">
+        <v>20260531</v>
+      </c>
+      <c r="C878" t="s">
+        <v>15</v>
+      </c>
+      <c r="D878">
+        <v>30</v>
+      </c>
+      <c r="E878">
+        <v>88.248999999999995</v>
+      </c>
+      <c r="F878">
+        <v>59.459000000000003</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A879" t="s">
+        <v>6</v>
+      </c>
+      <c r="B879">
+        <v>20260531</v>
+      </c>
+      <c r="C879" t="s">
+        <v>15</v>
+      </c>
+      <c r="D879">
+        <v>31</v>
+      </c>
+      <c r="E879">
+        <v>93.683000000000007</v>
+      </c>
+      <c r="F879">
+        <v>49.33</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A880" t="s">
+        <v>6</v>
+      </c>
+      <c r="B880">
+        <v>20260531</v>
+      </c>
+      <c r="C880" t="s">
+        <v>15</v>
+      </c>
+      <c r="D880">
+        <v>32</v>
+      </c>
+      <c r="E880">
+        <v>60.811999999999998</v>
+      </c>
+      <c r="F880">
+        <v>30.239000000000001</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A881" t="s">
+        <v>6</v>
+      </c>
+      <c r="B881">
+        <v>20260531</v>
+      </c>
+      <c r="C881" t="s">
+        <v>15</v>
+      </c>
+      <c r="D881">
+        <v>33</v>
+      </c>
+      <c r="E881">
+        <v>64.995000000000005</v>
+      </c>
+      <c r="F881">
+        <v>34.220999999999997</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A882" t="s">
+        <v>6</v>
+      </c>
+      <c r="B882">
+        <v>20260531</v>
+      </c>
+      <c r="C882" t="s">
+        <v>15</v>
+      </c>
+      <c r="D882">
+        <v>34</v>
+      </c>
+      <c r="E882">
+        <v>77.977000000000004</v>
+      </c>
+      <c r="F882">
+        <v>39.817999999999998</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A883" t="s">
+        <v>6</v>
+      </c>
+      <c r="B883">
+        <v>20260531</v>
+      </c>
+      <c r="C883" t="s">
+        <v>15</v>
+      </c>
+      <c r="D883">
+        <v>35</v>
+      </c>
+      <c r="E883">
+        <v>55.793999999999997</v>
+      </c>
+      <c r="F883">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A884" t="s">
+        <v>6</v>
+      </c>
+      <c r="B884">
+        <v>20260531</v>
+      </c>
+      <c r="C884" t="s">
+        <v>15</v>
+      </c>
+      <c r="D884">
+        <v>36</v>
+      </c>
+      <c r="E884">
+        <v>79.08</v>
+      </c>
+      <c r="F884">
+        <v>37.567999999999998</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A885" t="s">
+        <v>6</v>
+      </c>
+      <c r="B885">
+        <v>20260531</v>
+      </c>
+      <c r="C885" t="s">
+        <v>15</v>
+      </c>
+      <c r="D885">
+        <v>37</v>
+      </c>
+      <c r="E885">
+        <v>84.441000000000003</v>
+      </c>
+      <c r="F885">
+        <v>45.823</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A886" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886">
+        <v>20260531</v>
+      </c>
+      <c r="C886" t="s">
+        <v>15</v>
+      </c>
+      <c r="D886">
+        <v>38</v>
+      </c>
+      <c r="E886">
+        <v>92.072000000000003</v>
+      </c>
+      <c r="F886">
+        <v>43.234000000000002</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A887" t="s">
+        <v>6</v>
+      </c>
+      <c r="B887">
+        <v>20260531</v>
+      </c>
+      <c r="C887" t="s">
+        <v>15</v>
+      </c>
+      <c r="D887">
+        <v>39</v>
+      </c>
+      <c r="E887">
+        <v>81.716999999999999</v>
+      </c>
+      <c r="F887">
+        <v>54.951000000000001</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A888" t="s">
+        <v>6</v>
+      </c>
+      <c r="B888">
+        <v>20260531</v>
+      </c>
+      <c r="C888" t="s">
+        <v>15</v>
+      </c>
+      <c r="D888">
+        <v>40</v>
+      </c>
+      <c r="E888">
+        <v>117.002</v>
+      </c>
+      <c r="F888">
+        <v>43.878999999999998</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A889" t="s">
+        <v>6</v>
+      </c>
+      <c r="B889">
+        <v>20260531</v>
+      </c>
+      <c r="C889" t="s">
+        <v>15</v>
+      </c>
+      <c r="D889">
+        <v>41</v>
+      </c>
+      <c r="E889">
+        <v>108.64400000000001</v>
+      </c>
+      <c r="F889">
+        <v>54.609000000000002</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A890" t="s">
+        <v>6</v>
+      </c>
+      <c r="B890">
+        <v>20260531</v>
+      </c>
+      <c r="C890" t="s">
+        <v>15</v>
+      </c>
+      <c r="D890">
+        <v>42</v>
+      </c>
+      <c r="E890">
+        <v>87.302999999999997</v>
+      </c>
+      <c r="F890">
+        <v>53.786999999999999</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A891" t="s">
+        <v>6</v>
+      </c>
+      <c r="B891">
+        <v>20260531</v>
+      </c>
+      <c r="C891" t="s">
+        <v>15</v>
+      </c>
+      <c r="D891">
+        <v>43</v>
+      </c>
+      <c r="E891">
+        <v>85.948999999999998</v>
+      </c>
+      <c r="F891">
+        <v>49.307000000000002</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A892" t="s">
+        <v>6</v>
+      </c>
+      <c r="B892">
+        <v>20260531</v>
+      </c>
+      <c r="C892" t="s">
+        <v>15</v>
+      </c>
+      <c r="D892">
+        <v>44</v>
+      </c>
+      <c r="E892">
+        <v>103.441</v>
+      </c>
+      <c r="F892">
+        <v>49.353000000000002</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A893" t="s">
+        <v>6</v>
+      </c>
+      <c r="B893">
+        <v>20260531</v>
+      </c>
+      <c r="C893" t="s">
+        <v>15</v>
+      </c>
+      <c r="D893">
+        <v>45</v>
+      </c>
+      <c r="E893">
+        <v>104.776</v>
+      </c>
+      <c r="F893">
+        <v>45.435000000000002</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A894" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894">
+        <v>20260531</v>
+      </c>
+      <c r="C894" t="s">
+        <v>15</v>
+      </c>
+      <c r="D894">
+        <v>46</v>
+      </c>
+      <c r="E894">
+        <v>67.183000000000007</v>
+      </c>
+      <c r="F894">
+        <v>29.305</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A895" t="s">
+        <v>6</v>
+      </c>
+      <c r="B895">
+        <v>20260531</v>
+      </c>
+      <c r="C895" t="s">
+        <v>15</v>
+      </c>
+      <c r="D895">
+        <v>47</v>
+      </c>
+      <c r="E895">
+        <v>84.83</v>
+      </c>
+      <c r="F895">
+        <v>39.619999999999997</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A896" t="s">
+        <v>6</v>
+      </c>
+      <c r="B896">
+        <v>20260531</v>
+      </c>
+      <c r="C896" t="s">
+        <v>15</v>
+      </c>
+      <c r="D896">
+        <v>48</v>
+      </c>
+      <c r="E896">
+        <v>80.305000000000007</v>
+      </c>
+      <c r="F896">
+        <v>43.972999999999999</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A897" t="s">
+        <v>6</v>
+      </c>
+      <c r="B897">
+        <v>20260531</v>
+      </c>
+      <c r="C897" t="s">
+        <v>15</v>
+      </c>
+      <c r="D897">
+        <v>49</v>
+      </c>
+      <c r="E897">
+        <v>113.753</v>
+      </c>
+      <c r="F897">
+        <v>50.732999999999997</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A898" t="s">
+        <v>6</v>
+      </c>
+      <c r="B898">
+        <v>20260531</v>
+      </c>
+      <c r="C898" t="s">
+        <v>41</v>
+      </c>
+      <c r="D898">
+        <v>1</v>
+      </c>
+      <c r="E898">
+        <v>81.23</v>
+      </c>
+      <c r="F898">
+        <v>28.963000000000001</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A899" t="s">
+        <v>6</v>
+      </c>
+      <c r="B899">
+        <v>20260531</v>
+      </c>
+      <c r="C899" t="s">
+        <v>41</v>
+      </c>
+      <c r="D899">
+        <v>2</v>
+      </c>
+      <c r="E899">
+        <v>77.233000000000004</v>
+      </c>
+      <c r="F899">
+        <v>52.765000000000001</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A900" t="s">
+        <v>6</v>
+      </c>
+      <c r="B900">
+        <v>20260531</v>
+      </c>
+      <c r="C900" t="s">
+        <v>41</v>
+      </c>
+      <c r="D900">
+        <v>3</v>
+      </c>
+      <c r="E900">
+        <v>103.699</v>
+      </c>
+      <c r="F900">
+        <v>62.423000000000002</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A901" t="s">
+        <v>6</v>
+      </c>
+      <c r="B901">
+        <v>20260531</v>
+      </c>
+      <c r="C901" t="s">
+        <v>41</v>
+      </c>
+      <c r="D901">
+        <v>4</v>
+      </c>
+      <c r="E901">
+        <v>79.203000000000003</v>
+      </c>
+      <c r="F901">
+        <v>44.515000000000001</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A902" t="s">
+        <v>6</v>
+      </c>
+      <c r="B902">
+        <v>20260531</v>
+      </c>
+      <c r="C902" t="s">
+        <v>41</v>
+      </c>
+      <c r="D902">
+        <v>5</v>
+      </c>
+      <c r="E902">
+        <v>77.816000000000003</v>
+      </c>
+      <c r="F902">
+        <v>49.710999999999999</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A903" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903">
+        <v>20260531</v>
+      </c>
+      <c r="C903" t="s">
+        <v>41</v>
+      </c>
+      <c r="D903">
+        <v>6</v>
+      </c>
+      <c r="E903">
+        <v>75.370999999999995</v>
+      </c>
+      <c r="F903">
+        <v>27.62</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A904" t="s">
+        <v>6</v>
+      </c>
+      <c r="B904">
+        <v>20260531</v>
+      </c>
+      <c r="C904" t="s">
+        <v>41</v>
+      </c>
+      <c r="D904">
+        <v>7</v>
+      </c>
+      <c r="E904">
+        <v>101.84099999999999</v>
+      </c>
+      <c r="F904">
+        <v>61.957000000000001</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A905" t="s">
+        <v>6</v>
+      </c>
+      <c r="B905">
+        <v>20260531</v>
+      </c>
+      <c r="C905" t="s">
+        <v>41</v>
+      </c>
+      <c r="D905">
+        <v>8</v>
+      </c>
+      <c r="E905">
+        <v>104.336</v>
+      </c>
+      <c r="F905">
+        <v>48.116</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A906" t="s">
+        <v>6</v>
+      </c>
+      <c r="B906">
+        <v>20260531</v>
+      </c>
+      <c r="C906" t="s">
+        <v>41</v>
+      </c>
+      <c r="D906">
+        <v>9</v>
+      </c>
+      <c r="E906">
+        <v>97.16</v>
+      </c>
+      <c r="F906">
+        <v>50.598999999999997</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A907" t="s">
+        <v>6</v>
+      </c>
+      <c r="B907">
+        <v>20260531</v>
+      </c>
+      <c r="C907" t="s">
+        <v>41</v>
+      </c>
+      <c r="D907">
+        <v>10</v>
+      </c>
+      <c r="E907">
+        <v>74.010999999999996</v>
+      </c>
+      <c r="F907">
+        <v>44.984999999999999</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A908" t="s">
+        <v>6</v>
+      </c>
+      <c r="B908">
+        <v>20260531</v>
+      </c>
+      <c r="C908" t="s">
+        <v>41</v>
+      </c>
+      <c r="D908">
+        <v>11</v>
+      </c>
+      <c r="E908">
+        <v>83.823999999999998</v>
+      </c>
+      <c r="F908">
+        <v>45.259</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A909" t="s">
+        <v>6</v>
+      </c>
+      <c r="B909">
+        <v>20260531</v>
+      </c>
+      <c r="C909" t="s">
+        <v>41</v>
+      </c>
+      <c r="D909">
+        <v>12</v>
+      </c>
+      <c r="E909">
+        <v>62.927999999999997</v>
+      </c>
+      <c r="F909">
+        <v>44.600999999999999</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A910" t="s">
+        <v>6</v>
+      </c>
+      <c r="B910">
+        <v>20260531</v>
+      </c>
+      <c r="C910" t="s">
+        <v>41</v>
+      </c>
+      <c r="D910">
+        <v>13</v>
+      </c>
+      <c r="E910">
+        <v>95.885999999999996</v>
+      </c>
+      <c r="F910">
+        <v>32.222000000000001</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A911" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911">
+        <v>20260531</v>
+      </c>
+      <c r="C911" t="s">
+        <v>41</v>
+      </c>
+      <c r="D911">
+        <v>14</v>
+      </c>
+      <c r="E911">
+        <v>104.89100000000001</v>
+      </c>
+      <c r="F911">
+        <v>43.482999999999997</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A912" t="s">
+        <v>6</v>
+      </c>
+      <c r="B912">
+        <v>20260531</v>
+      </c>
+      <c r="C912" t="s">
+        <v>41</v>
+      </c>
+      <c r="D912">
+        <v>15</v>
+      </c>
+      <c r="E912">
+        <v>97.92</v>
+      </c>
+      <c r="F912">
+        <v>61.889000000000003</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A913" t="s">
+        <v>6</v>
+      </c>
+      <c r="B913">
+        <v>20260531</v>
+      </c>
+      <c r="C913" t="s">
+        <v>41</v>
+      </c>
+      <c r="D913">
+        <v>16</v>
+      </c>
+      <c r="E913">
+        <v>100.67</v>
+      </c>
+      <c r="F913">
+        <v>53.774999999999999</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A914" t="s">
+        <v>6</v>
+      </c>
+      <c r="B914">
+        <v>20260531</v>
+      </c>
+      <c r="C914" t="s">
+        <v>41</v>
+      </c>
+      <c r="D914">
+        <v>17</v>
+      </c>
+      <c r="E914">
+        <v>83.200999999999993</v>
+      </c>
+      <c r="F914">
+        <v>49.475999999999999</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A915" t="s">
+        <v>6</v>
+      </c>
+      <c r="B915">
+        <v>20260531</v>
+      </c>
+      <c r="C915" t="s">
+        <v>41</v>
+      </c>
+      <c r="D915">
+        <v>18</v>
+      </c>
+      <c r="E915">
+        <v>87.885999999999996</v>
+      </c>
+      <c r="F915">
+        <v>49.723999999999997</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A916" t="s">
+        <v>6</v>
+      </c>
+      <c r="B916">
+        <v>20260531</v>
+      </c>
+      <c r="C916" t="s">
+        <v>41</v>
+      </c>
+      <c r="D916">
+        <v>19</v>
+      </c>
+      <c r="E916">
+        <v>68.694999999999993</v>
+      </c>
+      <c r="F916">
+        <v>48.676000000000002</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A917" t="s">
+        <v>6</v>
+      </c>
+      <c r="B917">
+        <v>20260531</v>
+      </c>
+      <c r="C917" t="s">
+        <v>41</v>
+      </c>
+      <c r="D917">
+        <v>20</v>
+      </c>
+      <c r="E917">
+        <v>94.914000000000001</v>
+      </c>
+      <c r="F917">
+        <v>58.396999999999998</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A918" t="s">
+        <v>6</v>
+      </c>
+      <c r="B918">
+        <v>20260531</v>
+      </c>
+      <c r="C918" t="s">
+        <v>41</v>
+      </c>
+      <c r="D918">
+        <v>21</v>
+      </c>
+      <c r="E918">
+        <v>71.671999999999997</v>
+      </c>
+      <c r="F918">
+        <v>47.136000000000003</v>
+      </c>
+    </row>
+    <row r="919" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A919" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919">
+        <v>20260531</v>
+      </c>
+      <c r="C919" t="s">
+        <v>41</v>
+      </c>
+      <c r="D919">
+        <v>22</v>
+      </c>
+      <c r="E919">
+        <v>104.248</v>
+      </c>
+      <c r="F919">
+        <v>51.051000000000002</v>
+      </c>
+    </row>
+    <row r="920" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A920" t="s">
+        <v>6</v>
+      </c>
+      <c r="B920">
+        <v>20260531</v>
+      </c>
+      <c r="C920" t="s">
+        <v>41</v>
+      </c>
+      <c r="D920">
+        <v>23</v>
+      </c>
+      <c r="E920">
+        <v>124.568</v>
+      </c>
+      <c r="F920">
+        <v>52.692</v>
+      </c>
+    </row>
+    <row r="921" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A921" t="s">
+        <v>6</v>
+      </c>
+      <c r="B921">
+        <v>20260531</v>
+      </c>
+      <c r="C921" t="s">
+        <v>41</v>
+      </c>
+      <c r="D921">
+        <v>24</v>
+      </c>
+      <c r="E921">
+        <v>106.303</v>
+      </c>
+      <c r="F921">
+        <v>43.088999999999999</v>
+      </c>
+    </row>
+    <row r="922" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A922" t="s">
+        <v>6</v>
+      </c>
+      <c r="B922">
+        <v>20260531</v>
+      </c>
+      <c r="C922" t="s">
+        <v>41</v>
+      </c>
+      <c r="D922">
+        <v>25</v>
+      </c>
+      <c r="E922">
+        <v>111.08199999999999</v>
+      </c>
+      <c r="F922">
+        <v>46.912999999999997</v>
+      </c>
+    </row>
+    <row r="923" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A923" t="s">
+        <v>6</v>
+      </c>
+      <c r="B923">
+        <v>20260531</v>
+      </c>
+      <c r="C923" t="s">
+        <v>41</v>
+      </c>
+      <c r="D923">
+        <v>26</v>
+      </c>
+      <c r="E923">
+        <v>102.06100000000001</v>
+      </c>
+      <c r="F923">
+        <v>49.103999999999999</v>
+      </c>
+    </row>
+    <row r="924" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A924" t="s">
+        <v>6</v>
+      </c>
+      <c r="B924">
+        <v>20260531</v>
+      </c>
+      <c r="C924" t="s">
+        <v>41</v>
+      </c>
+      <c r="D924">
+        <v>27</v>
+      </c>
+      <c r="E924">
+        <v>96.796000000000006</v>
+      </c>
+      <c r="F924">
+        <v>47.865000000000002</v>
+      </c>
+    </row>
+    <row r="925" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A925" t="s">
+        <v>6</v>
+      </c>
+      <c r="B925">
+        <v>20260531</v>
+      </c>
+      <c r="C925" t="s">
+        <v>41</v>
+      </c>
+      <c r="D925">
+        <v>28</v>
+      </c>
+      <c r="E925">
+        <v>94.715999999999994</v>
+      </c>
+      <c r="F925">
+        <v>42.57</v>
+      </c>
+    </row>
+    <row r="926" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A926" t="s">
+        <v>6</v>
+      </c>
+      <c r="B926">
+        <v>20260531</v>
+      </c>
+      <c r="C926" t="s">
+        <v>41</v>
+      </c>
+      <c r="D926">
+        <v>29</v>
+      </c>
+      <c r="E926">
+        <v>67.843000000000004</v>
+      </c>
+      <c r="F926">
+        <v>38.61</v>
+      </c>
+    </row>
+    <row r="927" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A927" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927">
+        <v>20260531</v>
+      </c>
+      <c r="C927" t="s">
+        <v>41</v>
+      </c>
+      <c r="D927">
+        <v>30</v>
+      </c>
+      <c r="E927">
+        <v>95.527000000000001</v>
+      </c>
+      <c r="F927">
+        <v>43.469000000000001</v>
+      </c>
+    </row>
+    <row r="928" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A928" t="s">
+        <v>6</v>
+      </c>
+      <c r="B928">
+        <v>20260531</v>
+      </c>
+      <c r="C928" t="s">
+        <v>41</v>
+      </c>
+      <c r="D928">
+        <v>31</v>
+      </c>
+      <c r="E928">
+        <v>81.543999999999997</v>
+      </c>
+      <c r="F928">
+        <v>34.936</v>
+      </c>
+    </row>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A929" t="s">
+        <v>6</v>
+      </c>
+      <c r="B929">
+        <v>20260531</v>
+      </c>
+      <c r="C929" t="s">
+        <v>41</v>
+      </c>
+      <c r="D929">
+        <v>32</v>
+      </c>
+      <c r="E929">
+        <v>105.36</v>
+      </c>
+      <c r="F929">
+        <v>46.756999999999998</v>
+      </c>
+    </row>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A930" t="s">
+        <v>6</v>
+      </c>
+      <c r="B930">
+        <v>20260531</v>
+      </c>
+      <c r="C930" t="s">
+        <v>41</v>
+      </c>
+      <c r="D930">
+        <v>33</v>
+      </c>
+      <c r="E930">
+        <v>114.045</v>
+      </c>
+      <c r="F930">
+        <v>68.635000000000005</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A931" t="s">
+        <v>6</v>
+      </c>
+      <c r="B931">
+        <v>20260531</v>
+      </c>
+      <c r="C931" t="s">
+        <v>41</v>
+      </c>
+      <c r="D931">
+        <v>34</v>
+      </c>
+      <c r="E931">
+        <v>85.265000000000001</v>
+      </c>
+      <c r="F931">
+        <v>48.926000000000002</v>
+      </c>
+    </row>
+    <row r="932" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A932" t="s">
+        <v>6</v>
+      </c>
+      <c r="B932">
+        <v>20260531</v>
+      </c>
+      <c r="C932" t="s">
+        <v>41</v>
+      </c>
+      <c r="D932">
+        <v>35</v>
+      </c>
+      <c r="E932">
+        <v>100.706</v>
+      </c>
+      <c r="F932">
+        <v>62.462000000000003</v>
+      </c>
+    </row>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A933" t="s">
+        <v>6</v>
+      </c>
+      <c r="B933">
+        <v>20260531</v>
+      </c>
+      <c r="C933" t="s">
+        <v>41</v>
+      </c>
+      <c r="D933">
+        <v>36</v>
+      </c>
+      <c r="E933">
+        <v>108.27800000000001</v>
+      </c>
+      <c r="F933">
+        <v>56.024000000000001</v>
+      </c>
+    </row>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A934" t="s">
+        <v>6</v>
+      </c>
+      <c r="B934">
+        <v>20260531</v>
+      </c>
+      <c r="C934" t="s">
+        <v>41</v>
+      </c>
+      <c r="D934">
+        <v>37</v>
+      </c>
+      <c r="E934">
+        <v>123.84699999999999</v>
+      </c>
+      <c r="F934">
+        <v>62.143999999999998</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A935" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935">
+        <v>20260531</v>
+      </c>
+      <c r="C935" t="s">
+        <v>41</v>
+      </c>
+      <c r="D935">
+        <v>38</v>
+      </c>
+      <c r="E935">
+        <v>99.308999999999997</v>
+      </c>
+      <c r="F935">
+        <v>47.473999999999997</v>
+      </c>
+    </row>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A936" t="s">
+        <v>6</v>
+      </c>
+      <c r="B936">
+        <v>20260531</v>
+      </c>
+      <c r="C936" t="s">
+        <v>41</v>
+      </c>
+      <c r="D936">
+        <v>39</v>
+      </c>
+      <c r="E936">
+        <v>85.774000000000001</v>
+      </c>
+      <c r="F936">
+        <v>43.218000000000004</v>
+      </c>
+    </row>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A937" t="s">
+        <v>6</v>
+      </c>
+      <c r="B937">
+        <v>20260531</v>
+      </c>
+      <c r="C937" t="s">
+        <v>41</v>
+      </c>
+      <c r="D937">
+        <v>40</v>
+      </c>
+      <c r="E937">
+        <v>115.98699999999999</v>
+      </c>
+      <c r="F937">
+        <v>58.704000000000001</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A938" t="s">
+        <v>6</v>
+      </c>
+      <c r="B938">
+        <v>20260531</v>
+      </c>
+      <c r="C938" t="s">
+        <v>41</v>
+      </c>
+      <c r="D938">
+        <v>41</v>
+      </c>
+      <c r="E938">
+        <v>97.703999999999994</v>
+      </c>
+      <c r="F938">
+        <v>61.005000000000003</v>
+      </c>
+    </row>
+    <row r="939" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A939" t="s">
+        <v>6</v>
+      </c>
+      <c r="B939">
+        <v>20260531</v>
+      </c>
+      <c r="C939" t="s">
+        <v>41</v>
+      </c>
+      <c r="D939">
+        <v>42</v>
+      </c>
+      <c r="E939">
+        <v>100.979</v>
+      </c>
+      <c r="F939">
+        <v>54.786000000000001</v>
+      </c>
+    </row>
+    <row r="940" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A940" t="s">
+        <v>6</v>
+      </c>
+      <c r="B940">
+        <v>20260531</v>
+      </c>
+      <c r="C940" t="s">
+        <v>41</v>
+      </c>
+      <c r="D940">
+        <v>43</v>
+      </c>
+      <c r="E940">
+        <v>92.046000000000006</v>
+      </c>
+      <c r="F940">
+        <v>41.381</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>